--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$898</definedName>
@@ -54256,7 +54256,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-12 22:46</t>
+          <t>2026-10-13 06:25</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$898</definedName>
@@ -54256,7 +54256,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-13 06:25</t>
+          <t>2026-10-13 02:14</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -54256,7 +54256,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 03:45</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -54256,7 +54256,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-13 03:45</t>
+          <t>2026-10-13 04:26</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -54256,7 +54256,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-13 04:26</t>
+          <t>2026-10-13 04:46</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -54256,7 +54256,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-13 04:46</t>
+          <t>2026-10-13 05:06</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -54256,7 +54256,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-13 05:06</t>
+          <t>2026-10-13 05:29</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$898</definedName>
@@ -54256,7 +54256,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-13 05:29</t>
+          <t>2026-10-13 12:24</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$898</definedName>
@@ -54256,7 +54256,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-13 12:24</t>
+          <t>2026-10-13 08:42</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -54256,7 +54256,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-13 08:42</t>
+          <t>2026-10-13 09:42</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$894</definedName>
@@ -54024,7 +54024,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-13 13:17</t>
+          <t>2026-10-13 18:24</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$894</definedName>
@@ -54024,7 +54024,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-13 18:24</t>
+          <t>2026-10-13 14:49</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$894</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$893</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P894"/>
+  <dimension ref="A1:P893"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -40676,11 +40676,11 @@
     </row>
     <row r="671">
       <c r="A671" s="2" t="n">
-        <v>8980482818269</v>
+        <v>8980477116637</v>
       </c>
       <c r="B671" s="2" t="inlineStr">
         <is>
-          <t>Set de Candongas</t>
+          <t>Candongas en Covergold Rodinado</t>
         </is>
       </c>
       <c r="C671" s="2" t="inlineStr">
@@ -40719,12 +40719,12 @@
       </c>
       <c r="M671" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/set-de-topos-14</t>
+          <t>https://www.gavajoyeria.com/products/candongas-en-covergold-rodinado-17</t>
         </is>
       </c>
       <c r="N671" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/e4a8d0ed-8feb-4953-a2cb-57a996e4cf27.jpg?v=1745622264</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-01-15-at-3.47.38-PM.jpg?v=1745622246</t>
         </is>
       </c>
       <c r="O671" s="2" t="n">
@@ -40734,7 +40734,7 @@
     </row>
     <row r="672">
       <c r="A672" s="2" t="n">
-        <v>8980477116637</v>
+        <v>8980476854493</v>
       </c>
       <c r="B672" s="2" t="inlineStr">
         <is>
@@ -40777,22 +40777,22 @@
       </c>
       <c r="M672" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/candongas-en-covergold-rodinado-17</t>
+          <t>https://www.gavajoyeria.com/products/candongas-en-covergold-rodinado-43</t>
         </is>
       </c>
       <c r="N672" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-01-15-at-3.47.38-PM.jpg?v=1745622246</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/8839d738-dc15-418c-b9d8-c7488131de28-scaled.jpg?v=1745622246</t>
         </is>
       </c>
       <c r="O672" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P672" s="2" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" s="2" t="n">
-        <v>8980476854493</v>
+        <v>8980475642077</v>
       </c>
       <c r="B673" s="2" t="inlineStr">
         <is>
@@ -40835,40 +40835,40 @@
       </c>
       <c r="M673" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/candongas-en-covergold-rodinado-43</t>
+          <t>https://www.gavajoyeria.com/products/candongas-en-covergold-rodinado-9</t>
         </is>
       </c>
       <c r="N673" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/8839d738-dc15-418c-b9d8-c7488131de28-scaled.jpg?v=1745622246</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-01-15-at-3.05.29-PM.jpg?v=1745622242</t>
         </is>
       </c>
       <c r="O673" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P673" s="2" t="inlineStr"/>
     </row>
     <row r="674">
       <c r="A674" s="2" t="n">
-        <v>8980475642077</v>
+        <v>10192834134237</v>
       </c>
       <c r="B674" s="2" t="inlineStr">
         <is>
-          <t>Candongas en Covergold Rodinado</t>
+          <t>Set Collar en perla con dije con Corazón</t>
         </is>
       </c>
       <c r="C674" s="2" t="inlineStr">
         <is>
-          <t>Candongas</t>
+          <t>Choker</t>
         </is>
       </c>
       <c r="D674" s="2" t="inlineStr">
         <is>
-          <t>Candongas</t>
+          <t>Collares</t>
         </is>
       </c>
       <c r="E674" s="3" t="n">
-        <v>12000</v>
+        <v>95000</v>
       </c>
       <c r="F674" s="3" t="n"/>
       <c r="G674" s="3" t="n"/>
@@ -40883,7 +40883,7 @@
       </c>
       <c r="K674" s="2" t="inlineStr">
         <is>
-          <t>candongas</t>
+          <t>choker</t>
         </is>
       </c>
       <c r="L674" s="2" t="inlineStr">
@@ -40893,26 +40893,30 @@
       </c>
       <c r="M674" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/candongas-en-covergold-rodinado-9</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-en-rodio-copia-8</t>
         </is>
       </c>
       <c r="N674" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-01-15-at-3.05.29-PM.jpg?v=1745622242</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6298.jpg?v=1790041671</t>
         </is>
       </c>
       <c r="O674" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P674" s="2" t="inlineStr"/>
+      <c r="P674" s="2" t="inlineStr">
+        <is>
+          <t>Elegancia y delicadeza en una sola pieza. Nuestros collares de perlas con dije son el complemento perfecto para darle un toque sofisticado y femenino a cualquier look. MATERIAL Covergold con doble baño de rodio CUIDA TUS ACCESORIOS ✨ Para conservar su brillo y alargar su vida útil, ten en cuenta estos cuidados: • Evita el contacto con perfumes, sprays y productos químicos fuertes. • Guarda cada ac</t>
+        </is>
+      </c>
     </row>
     <row r="675">
       <c r="A675" s="2" t="n">
-        <v>10192834134237</v>
+        <v>9684186890461</v>
       </c>
       <c r="B675" s="2" t="inlineStr">
         <is>
-          <t>Set Collar en perla con dije con Corazón</t>
+          <t>Set de Collar en perla con dije en corazon</t>
         </is>
       </c>
       <c r="C675" s="2" t="inlineStr">
@@ -40926,7 +40930,7 @@
         </is>
       </c>
       <c r="E675" s="3" t="n">
-        <v>95000</v>
+        <v>94000</v>
       </c>
       <c r="F675" s="3" t="n"/>
       <c r="G675" s="3" t="n"/>
@@ -40951,12 +40955,12 @@
       </c>
       <c r="M675" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-en-rodio-copia-8</t>
+          <t>https://www.gavajoyeria.com/products/set-de-collar-en-perla-con-dije-en-corazon</t>
         </is>
       </c>
       <c r="N675" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6298.jpg?v=1790041671</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6251.jpg?v=1790038922</t>
         </is>
       </c>
       <c r="O675" s="2" t="n">
@@ -40970,7 +40974,7 @@
     </row>
     <row r="676">
       <c r="A676" s="2" t="n">
-        <v>9684186890461</v>
+        <v>9684122697949</v>
       </c>
       <c r="B676" s="2" t="inlineStr">
         <is>
@@ -41013,12 +41017,12 @@
       </c>
       <c r="M676" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/set-de-collar-en-perla-con-dije-en-corazon</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-en-rodio-copia-7</t>
         </is>
       </c>
       <c r="N676" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6251.jpg?v=1790038922</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6230.jpg?v=1790037164</t>
         </is>
       </c>
       <c r="O676" s="2" t="n">
@@ -41032,11 +41036,11 @@
     </row>
     <row r="677">
       <c r="A677" s="2" t="n">
-        <v>9684122697949</v>
+        <v>10192829022429</v>
       </c>
       <c r="B677" s="2" t="inlineStr">
         <is>
-          <t>Set de Collar en perla con dije en corazon</t>
+          <t>Collar en perla con dije nacar</t>
         </is>
       </c>
       <c r="C677" s="2" t="inlineStr">
@@ -41050,7 +41054,7 @@
         </is>
       </c>
       <c r="E677" s="3" t="n">
-        <v>94000</v>
+        <v>92000</v>
       </c>
       <c r="F677" s="3" t="n"/>
       <c r="G677" s="3" t="n"/>
@@ -41075,12 +41079,12 @@
       </c>
       <c r="M677" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-en-rodio-copia-7</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-religioso-copia-2</t>
         </is>
       </c>
       <c r="N677" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6230.jpg?v=1790037164</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6290.jpg?v=1790041671</t>
         </is>
       </c>
       <c r="O677" s="2" t="n">
@@ -41094,11 +41098,11 @@
     </row>
     <row r="678">
       <c r="A678" s="2" t="n">
-        <v>10192829022429</v>
+        <v>9684203241693</v>
       </c>
       <c r="B678" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije nacar</t>
+          <t>Collar en perla con dije de corazon</t>
         </is>
       </c>
       <c r="C678" s="2" t="inlineStr">
@@ -41137,12 +41141,12 @@
       </c>
       <c r="M678" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-religioso-copia-2</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-rodio-con-maxi-aretes-copia</t>
         </is>
       </c>
       <c r="N678" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6290.jpg?v=1790041671</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6267.jpg?v=1790038922</t>
         </is>
       </c>
       <c r="O678" s="2" t="n">
@@ -41156,11 +41160,11 @@
     </row>
     <row r="679">
       <c r="A679" s="2" t="n">
-        <v>9684203241693</v>
+        <v>9684125253853</v>
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije de corazon</t>
+          <t>Collar en perla con dije de flor en nacar</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -41199,12 +41203,12 @@
       </c>
       <c r="M679" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-rodio-con-maxi-aretes-copia</t>
+          <t>https://www.gavajoyeria.com/products/set-de-collar-en-perla-con-dije-en-corazon-copia</t>
         </is>
       </c>
       <c r="N679" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6267.jpg?v=1790038922</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6231.jpg?v=1790037164</t>
         </is>
       </c>
       <c r="O679" s="2" t="n">
@@ -41218,11 +41222,11 @@
     </row>
     <row r="680">
       <c r="A680" s="2" t="n">
-        <v>9684125253853</v>
+        <v>8980472627421</v>
       </c>
       <c r="B680" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije de flor en nacar</t>
+          <t>Collar de Escarabajo y Mariquita</t>
         </is>
       </c>
       <c r="C680" s="2" t="inlineStr">
@@ -41236,7 +41240,7 @@
         </is>
       </c>
       <c r="E680" s="3" t="n">
-        <v>92000</v>
+        <v>87000</v>
       </c>
       <c r="F680" s="3" t="n"/>
       <c r="G680" s="3" t="n"/>
@@ -41261,30 +41265,26 @@
       </c>
       <c r="M680" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/set-de-collar-en-perla-con-dije-en-corazon-copia</t>
+          <t>https://www.gavajoyeria.com/products/collar-de-escarabajo-y-mariquita</t>
         </is>
       </c>
       <c r="N680" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6231.jpg?v=1790037164</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-14-at-4.29.19-PM.jpg?v=1745622231</t>
         </is>
       </c>
       <c r="O680" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P680" s="2" t="inlineStr">
-        <is>
-          <t>Elegancia y delicadeza en una sola pieza. Nuestros collares de perlas con dije son el complemento perfecto para darle un toque sofisticado y femenino a cualquier look. MATERIAL Covergold con doble baño de rodio CUIDA TUS ACCESORIOS ✨ Para conservar su brillo y alargar su vida útil, ten en cuenta estos cuidados: • Evita el contacto con perfumes, sprays y productos químicos fuertes. • Guarda cada ac</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="P680" s="2" t="inlineStr"/>
     </row>
     <row r="681">
       <c r="A681" s="2" t="n">
-        <v>8980472627421</v>
+        <v>10192820994269</v>
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>Collar de Escarabajo y Mariquita</t>
+          <t>Collar en perla con dije religioso</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
@@ -41298,7 +41298,7 @@
         </is>
       </c>
       <c r="E681" s="3" t="n">
-        <v>87000</v>
+        <v>85000</v>
       </c>
       <c r="F681" s="3" t="n"/>
       <c r="G681" s="3" t="n"/>
@@ -41323,26 +41323,30 @@
       </c>
       <c r="M681" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-de-escarabajo-y-mariquita</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-corazon-copia-2</t>
         </is>
       </c>
       <c r="N681" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-14-at-4.29.19-PM.jpg?v=1745622231</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6286.jpg?v=1790041671</t>
         </is>
       </c>
       <c r="O681" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P681" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P681" s="2" t="inlineStr">
+        <is>
+          <t>Elegancia y delicadeza en una sola pieza. Nuestros collares de perlas con dije son el complemento perfecto para darle un toque sofisticado y femenino a cualquier look. MATERIAL Covergold con doble baño de rodio CUIDA TUS ACCESORIOS ✨ Para conservar su brillo y alargar su vida útil, ten en cuenta estos cuidados: • Evita el contacto con perfumes, sprays y productos químicos fuertes. • Guarda cada ac</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="A682" s="2" t="n">
-        <v>10192820994269</v>
+        <v>9684188004573</v>
       </c>
       <c r="B682" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije religioso</t>
+          <t>Collar en perla con dije Religioso</t>
         </is>
       </c>
       <c r="C682" s="2" t="inlineStr">
@@ -41356,7 +41360,7 @@
         </is>
       </c>
       <c r="E682" s="3" t="n">
-        <v>85000</v>
+        <v>84000</v>
       </c>
       <c r="F682" s="3" t="n"/>
       <c r="G682" s="3" t="n"/>
@@ -41381,12 +41385,12 @@
       </c>
       <c r="M682" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-corazon-copia-2</t>
+          <t>https://www.gavajoyeria.com/products/set-de-collar-en-perla-con-dije-en-corazon-copia-1</t>
         </is>
       </c>
       <c r="N682" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6286.jpg?v=1790041671</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6252.jpg?v=1790038922</t>
         </is>
       </c>
       <c r="O682" s="2" t="n">
@@ -41400,11 +41404,11 @@
     </row>
     <row r="683">
       <c r="A683" s="2" t="n">
-        <v>9684188004573</v>
+        <v>10192840261853</v>
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije Religioso</t>
+          <t>Collar en perla con dije de flores</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -41418,7 +41422,7 @@
         </is>
       </c>
       <c r="E683" s="3" t="n">
-        <v>84000</v>
+        <v>82000</v>
       </c>
       <c r="F683" s="3" t="n"/>
       <c r="G683" s="3" t="n"/>
@@ -41443,12 +41447,12 @@
       </c>
       <c r="M683" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/set-de-collar-en-perla-con-dije-en-corazon-copia-1</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-flores-copia-1</t>
         </is>
       </c>
       <c r="N683" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6252.jpg?v=1790038922</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6320.jpg?v=1790041671</t>
         </is>
       </c>
       <c r="O683" s="2" t="n">
@@ -41462,7 +41466,7 @@
     </row>
     <row r="684">
       <c r="A684" s="2" t="n">
-        <v>10192840261853</v>
+        <v>10192840032477</v>
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
@@ -41505,12 +41509,12 @@
       </c>
       <c r="M684" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-flores-copia-1</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-hoja-copia</t>
         </is>
       </c>
       <c r="N684" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6320.jpg?v=1790041671</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6312.jpg?v=1790041671</t>
         </is>
       </c>
       <c r="O684" s="2" t="n">
@@ -41524,11 +41528,11 @@
     </row>
     <row r="685">
       <c r="A685" s="2" t="n">
-        <v>10192840032477</v>
+        <v>10192838951133</v>
       </c>
       <c r="B685" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije de flores</t>
+          <t>Collar en perla con dije de hoja</t>
         </is>
       </c>
       <c r="C685" s="2" t="inlineStr">
@@ -41567,12 +41571,12 @@
       </c>
       <c r="M685" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-hoja-copia</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-nacar-copia</t>
         </is>
       </c>
       <c r="N685" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6312.jpg?v=1790041671</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6309.jpg?v=1790041671</t>
         </is>
       </c>
       <c r="O685" s="2" t="n">
@@ -41586,11 +41590,11 @@
     </row>
     <row r="686">
       <c r="A686" s="2" t="n">
-        <v>10192838951133</v>
+        <v>10192819093725</v>
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije de hoja</t>
+          <t>Collar en perla con dije en rodio</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -41629,12 +41633,12 @@
       </c>
       <c r="M686" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-nacar-copia</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-corazon-copia-1</t>
         </is>
       </c>
       <c r="N686" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6309.jpg?v=1790041671</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6280.jpg?v=1790041671</t>
         </is>
       </c>
       <c r="O686" s="2" t="n">
@@ -41648,11 +41652,11 @@
     </row>
     <row r="687">
       <c r="A687" s="2" t="n">
-        <v>10192819093725</v>
+        <v>9684199375069</v>
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije en rodio</t>
+          <t>Collar en perla con dije de rodio</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
@@ -41691,12 +41695,12 @@
       </c>
       <c r="M687" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-corazon-copia-1</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-rodio-copia</t>
         </is>
       </c>
       <c r="N687" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6280.jpg?v=1790041671</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6263.jpg?v=1790038922</t>
         </is>
       </c>
       <c r="O687" s="2" t="n">
@@ -41710,11 +41714,11 @@
     </row>
     <row r="688">
       <c r="A688" s="2" t="n">
-        <v>9684199375069</v>
+        <v>9684194558173</v>
       </c>
       <c r="B688" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije de rodio</t>
+          <t>Collar en perla con dije de flores</t>
         </is>
       </c>
       <c r="C688" s="2" t="inlineStr">
@@ -41753,12 +41757,12 @@
       </c>
       <c r="M688" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-rodio-copia</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-en-rodio-flor-copia</t>
         </is>
       </c>
       <c r="N688" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6263.jpg?v=1790038922</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6259.jpg?v=1790038922</t>
         </is>
       </c>
       <c r="O688" s="2" t="n">
@@ -41772,11 +41776,11 @@
     </row>
     <row r="689">
       <c r="A689" s="2" t="n">
-        <v>9684194558173</v>
+        <v>9684193116381</v>
       </c>
       <c r="B689" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije de flores</t>
+          <t>Collar en perla con dije en rodio flor</t>
         </is>
       </c>
       <c r="C689" s="2" t="inlineStr">
@@ -41815,12 +41819,12 @@
       </c>
       <c r="M689" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-en-rodio-flor-copia</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-religioso-copia-1</t>
         </is>
       </c>
       <c r="N689" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6259.jpg?v=1790038922</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6256.jpg?v=1790038922</t>
         </is>
       </c>
       <c r="O689" s="2" t="n">
@@ -41834,11 +41838,11 @@
     </row>
     <row r="690">
       <c r="A690" s="2" t="n">
-        <v>9684193116381</v>
+        <v>9684181450973</v>
       </c>
       <c r="B690" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije en rodio flor</t>
+          <t>Collar en perla con dije de cruz con perlas</t>
         </is>
       </c>
       <c r="C690" s="2" t="inlineStr">
@@ -41877,12 +41881,12 @@
       </c>
       <c r="M690" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-religioso-copia-1</t>
+          <t>https://www.gavajoyeria.com/products/set-de-collar-en-perla-con-dije-de-cruz-con-perla-copia</t>
         </is>
       </c>
       <c r="N690" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6256.jpg?v=1790038922</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6246.jpg?v=1790038922</t>
         </is>
       </c>
       <c r="O690" s="2" t="n">
@@ -41896,11 +41900,11 @@
     </row>
     <row r="691">
       <c r="A691" s="2" t="n">
-        <v>9684181450973</v>
+        <v>9684177649885</v>
       </c>
       <c r="B691" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije de cruz con perlas</t>
+          <t>Collar en perla con dije de media flor</t>
         </is>
       </c>
       <c r="C691" s="2" t="inlineStr">
@@ -41939,12 +41943,12 @@
       </c>
       <c r="M691" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/set-de-collar-en-perla-con-dije-de-cruz-con-perla-copia</t>
+          <t>https://www.gavajoyeria.com/products/set-de-collar-en-perla-con-dije-de-hoja-de-otono-copia</t>
         </is>
       </c>
       <c r="N691" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6246.jpg?v=1790038922</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6242.jpg?v=1790038922</t>
         </is>
       </c>
       <c r="O691" s="2" t="n">
@@ -41958,11 +41962,11 @@
     </row>
     <row r="692">
       <c r="A692" s="2" t="n">
-        <v>9684177649885</v>
+        <v>9684176306397</v>
       </c>
       <c r="B692" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije de media flor</t>
+          <t>Collar en perla con dije de hoja de otoño</t>
         </is>
       </c>
       <c r="C692" s="2" t="inlineStr">
@@ -42001,12 +42005,12 @@
       </c>
       <c r="M692" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/set-de-collar-en-perla-con-dije-de-hoja-de-otono-copia</t>
+          <t>https://www.gavajoyeria.com/products/set-de-collar-en-perla-con-dije-de-flor-copia</t>
         </is>
       </c>
       <c r="N692" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6242.jpg?v=1790038922</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6238.jpg?v=1790038922</t>
         </is>
       </c>
       <c r="O692" s="2" t="n">
@@ -42020,11 +42024,11 @@
     </row>
     <row r="693">
       <c r="A693" s="2" t="n">
-        <v>9684176306397</v>
+        <v>9684171096285</v>
       </c>
       <c r="B693" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije de hoja de otoño</t>
+          <t>Collar en perla con dije de hoja</t>
         </is>
       </c>
       <c r="C693" s="2" t="inlineStr">
@@ -42063,12 +42067,12 @@
       </c>
       <c r="M693" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/set-de-collar-en-perla-con-dije-de-flor-copia</t>
+          <t>https://www.gavajoyeria.com/products/set-de-collar-en-perla-con-dije-de-flor-en-nacar-copia</t>
         </is>
       </c>
       <c r="N693" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6238.jpg?v=1790038922</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6235.jpg?v=1790038922</t>
         </is>
       </c>
       <c r="O693" s="2" t="n">
@@ -42082,11 +42086,11 @@
     </row>
     <row r="694">
       <c r="A694" s="2" t="n">
-        <v>9684171096285</v>
+        <v>9684117192925</v>
       </c>
       <c r="B694" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije de hoja</t>
+          <t>Collar en perla con dije en rodio</t>
         </is>
       </c>
       <c r="C694" s="2" t="inlineStr">
@@ -42125,12 +42129,12 @@
       </c>
       <c r="M694" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/set-de-collar-en-perla-con-dije-de-flor-en-nacar-copia</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-en-rodio-copia-5</t>
         </is>
       </c>
       <c r="N694" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6235.jpg?v=1790038922</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6226.jpg?v=1790037164</t>
         </is>
       </c>
       <c r="O694" s="2" t="n">
@@ -42144,7 +42148,7 @@
     </row>
     <row r="695">
       <c r="A695" s="2" t="n">
-        <v>9684117192925</v>
+        <v>9684115357917</v>
       </c>
       <c r="B695" s="2" t="inlineStr">
         <is>
@@ -42187,12 +42191,12 @@
       </c>
       <c r="M695" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-en-rodio-copia-5</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-en-rodio-de-flor-copia</t>
         </is>
       </c>
       <c r="N695" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6226.jpg?v=1790037164</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6223.jpg?v=1790037164</t>
         </is>
       </c>
       <c r="O695" s="2" t="n">
@@ -42206,11 +42210,11 @@
     </row>
     <row r="696">
       <c r="A696" s="2" t="n">
-        <v>9684115357917</v>
+        <v>9684111786205</v>
       </c>
       <c r="B696" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije en rodio</t>
+          <t>Collar en perla con dije en rodio de flor</t>
         </is>
       </c>
       <c r="C696" s="2" t="inlineStr">
@@ -42249,12 +42253,12 @@
       </c>
       <c r="M696" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-en-rodio-de-flor-copia</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-en-rodio-virgen-de-guadalupe-copia</t>
         </is>
       </c>
       <c r="N696" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6223.jpg?v=1790037164</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6222.jpg?v=1790037164</t>
         </is>
       </c>
       <c r="O696" s="2" t="n">
@@ -42268,11 +42272,11 @@
     </row>
     <row r="697">
       <c r="A697" s="2" t="n">
-        <v>9684111786205</v>
+        <v>9684108345565</v>
       </c>
       <c r="B697" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije en rodio de flor</t>
+          <t>Collar en perla con dije en rodio</t>
         </is>
       </c>
       <c r="C697" s="2" t="inlineStr">
@@ -42311,12 +42315,12 @@
       </c>
       <c r="M697" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-en-rodio-virgen-de-guadalupe-copia</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-en-rodio-copia-2</t>
         </is>
       </c>
       <c r="N697" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6222.jpg?v=1790037164</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6215_bf7f9f41-6c2c-4a10-ac21-dfc844a20f87.jpg?v=1790037164</t>
         </is>
       </c>
       <c r="O697" s="2" t="n">
@@ -42330,7 +42334,7 @@
     </row>
     <row r="698">
       <c r="A698" s="2" t="n">
-        <v>9684108345565</v>
+        <v>9684107264221</v>
       </c>
       <c r="B698" s="2" t="inlineStr">
         <is>
@@ -42373,12 +42377,12 @@
       </c>
       <c r="M698" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-en-rodio-copia-2</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-en-rodio-copia-1</t>
         </is>
       </c>
       <c r="N698" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6215_bf7f9f41-6c2c-4a10-ac21-dfc844a20f87.jpg?v=1790037164</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6214.jpg?v=1790037164</t>
         </is>
       </c>
       <c r="O698" s="2" t="n">
@@ -42392,7 +42396,7 @@
     </row>
     <row r="699">
       <c r="A699" s="2" t="n">
-        <v>9684107264221</v>
+        <v>9684103037149</v>
       </c>
       <c r="B699" s="2" t="inlineStr">
         <is>
@@ -42435,12 +42439,12 @@
       </c>
       <c r="M699" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-en-rodio-copia-1</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-circulos-copia</t>
         </is>
       </c>
       <c r="N699" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6214.jpg?v=1790037164</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6210.jpg?v=1790037164</t>
         </is>
       </c>
       <c r="O699" s="2" t="n">
@@ -42454,11 +42458,11 @@
     </row>
     <row r="700">
       <c r="A700" s="2" t="n">
-        <v>9684103037149</v>
+        <v>9684100382941</v>
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije en rodio</t>
+          <t>Collar en perla con dije de circulos</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -42497,12 +42501,12 @@
       </c>
       <c r="M700" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-circulos-copia</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-dos-cirulos-copia</t>
         </is>
       </c>
       <c r="N700" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6210.jpg?v=1790037164</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6207.jpg?v=1790037165</t>
         </is>
       </c>
       <c r="O700" s="2" t="n">
@@ -42516,11 +42520,11 @@
     </row>
     <row r="701">
       <c r="A701" s="2" t="n">
-        <v>9684100382941</v>
+        <v>9684099268829</v>
       </c>
       <c r="B701" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije de circulos</t>
+          <t>Collar en perla con dije de dos cirulos</t>
         </is>
       </c>
       <c r="C701" s="2" t="inlineStr">
@@ -42559,12 +42563,12 @@
       </c>
       <c r="M701" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-dos-cirulos-copia</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-tres-cirulos-copia</t>
         </is>
       </c>
       <c r="N701" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6207.jpg?v=1790037165</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6206.jpg?v=1790037164</t>
         </is>
       </c>
       <c r="O701" s="2" t="n">
@@ -42578,11 +42582,11 @@
     </row>
     <row r="702">
       <c r="A702" s="2" t="n">
-        <v>9684099268829</v>
+        <v>9684179452125</v>
       </c>
       <c r="B702" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije de dos cirulos</t>
+          <t>Collar en perla con dije de cruz con perla</t>
         </is>
       </c>
       <c r="C702" s="2" t="inlineStr">
@@ -42596,7 +42600,7 @@
         </is>
       </c>
       <c r="E702" s="3" t="n">
-        <v>82000</v>
+        <v>80000</v>
       </c>
       <c r="F702" s="3" t="n"/>
       <c r="G702" s="3" t="n"/>
@@ -42621,12 +42625,12 @@
       </c>
       <c r="M702" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-tres-cirulos-copia</t>
+          <t>https://www.gavajoyeria.com/products/set-de-collar-en-perla-con-dije-de-media-flor-copia</t>
         </is>
       </c>
       <c r="N702" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6206.jpg?v=1790037164</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6243.jpg?v=1790038922</t>
         </is>
       </c>
       <c r="O702" s="2" t="n">
@@ -42640,11 +42644,11 @@
     </row>
     <row r="703">
       <c r="A703" s="2" t="n">
-        <v>9684179452125</v>
+        <v>10192836853981</v>
       </c>
       <c r="B703" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije de cruz con perla</t>
+          <t>Collar en perla con dije de nacar</t>
         </is>
       </c>
       <c r="C703" s="2" t="inlineStr">
@@ -42658,7 +42662,7 @@
         </is>
       </c>
       <c r="E703" s="3" t="n">
-        <v>80000</v>
+        <v>79000</v>
       </c>
       <c r="F703" s="3" t="n"/>
       <c r="G703" s="3" t="n"/>
@@ -42683,12 +42687,12 @@
       </c>
       <c r="M703" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/set-de-collar-en-perla-con-dije-de-media-flor-copia</t>
+          <t>https://www.gavajoyeria.com/products/set-collar-en-perla-con-dije-con-corazon-copia</t>
         </is>
       </c>
       <c r="N703" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6243.jpg?v=1790038922</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6304.jpg?v=1790041671</t>
         </is>
       </c>
       <c r="O703" s="2" t="n">
@@ -42702,11 +42706,11 @@
     </row>
     <row r="704">
       <c r="A704" s="2" t="n">
-        <v>10192836853981</v>
+        <v>9684173357277</v>
       </c>
       <c r="B704" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije de nacar</t>
+          <t>Collar en perla con dije de flor</t>
         </is>
       </c>
       <c r="C704" s="2" t="inlineStr">
@@ -42745,12 +42749,12 @@
       </c>
       <c r="M704" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/set-collar-en-perla-con-dije-con-corazon-copia</t>
+          <t>https://www.gavajoyeria.com/products/set-de-collar-en-perla-con-dije-de-hoja-copia</t>
         </is>
       </c>
       <c r="N704" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6304.jpg?v=1790041671</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6238.jpg?v=1790038922</t>
         </is>
       </c>
       <c r="O704" s="2" t="n">
@@ -42764,11 +42768,11 @@
     </row>
     <row r="705">
       <c r="A705" s="2" t="n">
-        <v>9684173357277</v>
+        <v>8980471709917</v>
       </c>
       <c r="B705" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije de flor</t>
+          <t>Collar de Libélula</t>
         </is>
       </c>
       <c r="C705" s="2" t="inlineStr">
@@ -42807,30 +42811,26 @@
       </c>
       <c r="M705" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/set-de-collar-en-perla-con-dije-de-hoja-copia</t>
+          <t>https://www.gavajoyeria.com/products/collar-de-libelula-6</t>
         </is>
       </c>
       <c r="N705" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6238.jpg?v=1790038922</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.46-PM.jpg?v=1745622227</t>
         </is>
       </c>
       <c r="O705" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P705" s="2" t="inlineStr">
-        <is>
-          <t>Elegancia y delicadeza en una sola pieza. Nuestros collares de perlas con dije son el complemento perfecto para darle un toque sofisticado y femenino a cualquier look. MATERIAL Covergold con doble baño de rodio CUIDA TUS ACCESORIOS ✨ Para conservar su brillo y alargar su vida útil, ten en cuenta estos cuidados: • Evita el contacto con perfumes, sprays y productos químicos fuertes. • Guarda cada ac</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P705" s="2" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" s="2" t="n">
-        <v>8980471709917</v>
+        <v>8980471480541</v>
       </c>
       <c r="B706" s="2" t="inlineStr">
         <is>
-          <t>Collar de Libélula</t>
+          <t>Collar de Escarabajo</t>
         </is>
       </c>
       <c r="C706" s="2" t="inlineStr">
@@ -42869,12 +42869,12 @@
       </c>
       <c r="M706" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-de-libelula-6</t>
+          <t>https://www.gavajoyeria.com/products/collar-de-escarabajo-3</t>
         </is>
       </c>
       <c r="N706" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.46-PM.jpg?v=1745622227</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.47-PM-5.jpg?v=1745622226</t>
         </is>
       </c>
       <c r="O706" s="2" t="n">
@@ -42884,11 +42884,11 @@
     </row>
     <row r="707">
       <c r="A707" s="2" t="n">
-        <v>8980471480541</v>
+        <v>8980471349469</v>
       </c>
       <c r="B707" s="2" t="inlineStr">
         <is>
-          <t>Collar de Escarabajo</t>
+          <t>Collar de Mariquita</t>
         </is>
       </c>
       <c r="C707" s="2" t="inlineStr">
@@ -42927,12 +42927,12 @@
       </c>
       <c r="M707" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-de-escarabajo-3</t>
+          <t>https://www.gavajoyeria.com/products/collar-de-mariquita-4</t>
         </is>
       </c>
       <c r="N707" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.47-PM-5.jpg?v=1745622226</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.12.36-PM.jpg?v=1745622226</t>
         </is>
       </c>
       <c r="O707" s="2" t="n">
@@ -42942,11 +42942,11 @@
     </row>
     <row r="708">
       <c r="A708" s="2" t="n">
-        <v>8980471349469</v>
+        <v>8980471546077</v>
       </c>
       <c r="B708" s="2" t="inlineStr">
         <is>
-          <t>Collar de Mariquita</t>
+          <t>Collar de Libélula</t>
         </is>
       </c>
       <c r="C708" s="2" t="inlineStr">
@@ -42985,12 +42985,12 @@
       </c>
       <c r="M708" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-de-mariquita-4</t>
+          <t>https://www.gavajoyeria.com/products/collar-de-libelula-5</t>
         </is>
       </c>
       <c r="N708" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.12.36-PM.jpg?v=1745622226</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.47-PM.jpg?v=1745622227</t>
         </is>
       </c>
       <c r="O708" s="2" t="n">
@@ -43000,11 +43000,11 @@
     </row>
     <row r="709">
       <c r="A709" s="2" t="n">
-        <v>8980471546077</v>
+        <v>8980471316701</v>
       </c>
       <c r="B709" s="2" t="inlineStr">
         <is>
-          <t>Collar de Libélula</t>
+          <t>Collar de Escarabajo</t>
         </is>
       </c>
       <c r="C709" s="2" t="inlineStr">
@@ -43043,12 +43043,12 @@
       </c>
       <c r="M709" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-de-libelula-5</t>
+          <t>https://www.gavajoyeria.com/products/collar-de-escarabajo-5</t>
         </is>
       </c>
       <c r="N709" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.47-PM.jpg?v=1745622227</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.48-PM.jpg?v=1745622226</t>
         </is>
       </c>
       <c r="O709" s="2" t="n">
@@ -43058,11 +43058,11 @@
     </row>
     <row r="710">
       <c r="A710" s="2" t="n">
-        <v>8980471316701</v>
+        <v>8980471218397</v>
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>Collar de Escarabajo</t>
+          <t>Collar de Mariquita</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -43101,12 +43101,12 @@
       </c>
       <c r="M710" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-de-escarabajo-5</t>
+          <t>https://www.gavajoyeria.com/products/collar-de-mariquita-5</t>
         </is>
       </c>
       <c r="N710" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.48-PM.jpg?v=1745622226</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.12.36-PM-2.jpg?v=1745622225</t>
         </is>
       </c>
       <c r="O710" s="2" t="n">
@@ -43116,11 +43116,11 @@
     </row>
     <row r="711">
       <c r="A711" s="2" t="n">
-        <v>8980471218397</v>
+        <v>8980471152861</v>
       </c>
       <c r="B711" s="2" t="inlineStr">
         <is>
-          <t>Collar de Mariquita</t>
+          <t>Collar de Libélula</t>
         </is>
       </c>
       <c r="C711" s="2" t="inlineStr">
@@ -43159,12 +43159,12 @@
       </c>
       <c r="M711" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-de-mariquita-5</t>
+          <t>https://www.gavajoyeria.com/products/collar-de-libelula-8</t>
         </is>
       </c>
       <c r="N711" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.12.36-PM-2.jpg?v=1745622225</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.42-PM.jpg?v=1745622225</t>
         </is>
       </c>
       <c r="O711" s="2" t="n">
@@ -43174,11 +43174,11 @@
     </row>
     <row r="712">
       <c r="A712" s="2" t="n">
-        <v>8980471152861</v>
+        <v>8980470857949</v>
       </c>
       <c r="B712" s="2" t="inlineStr">
         <is>
-          <t>Collar de Libélula</t>
+          <t>Collar de Escarabajo</t>
         </is>
       </c>
       <c r="C712" s="2" t="inlineStr">
@@ -43217,12 +43217,12 @@
       </c>
       <c r="M712" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-de-libelula-8</t>
+          <t>https://www.gavajoyeria.com/products/collar-de-escarabajo-2</t>
         </is>
       </c>
       <c r="N712" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.42-PM.jpg?v=1745622225</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.47-PM-3.jpg?v=1745622224</t>
         </is>
       </c>
       <c r="O712" s="2" t="n">
@@ -43232,11 +43232,11 @@
     </row>
     <row r="713">
       <c r="A713" s="2" t="n">
-        <v>8980470857949</v>
+        <v>8980471644381</v>
       </c>
       <c r="B713" s="2" t="inlineStr">
         <is>
-          <t>Collar de Escarabajo</t>
+          <t>Collar de Libélula</t>
         </is>
       </c>
       <c r="C713" s="2" t="inlineStr">
@@ -43275,12 +43275,12 @@
       </c>
       <c r="M713" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-de-escarabajo-2</t>
+          <t>https://www.gavajoyeria.com/products/collar-de-libelula-4</t>
         </is>
       </c>
       <c r="N713" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.47-PM-3.jpg?v=1745622224</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.47-PM-1.jpg?v=1745622227</t>
         </is>
       </c>
       <c r="O713" s="2" t="n">
@@ -43290,7 +43290,7 @@
     </row>
     <row r="714">
       <c r="A714" s="2" t="n">
-        <v>8980471644381</v>
+        <v>8980471578845</v>
       </c>
       <c r="B714" s="2" t="inlineStr">
         <is>
@@ -43333,12 +43333,12 @@
       </c>
       <c r="M714" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-de-libelula-4</t>
+          <t>https://www.gavajoyeria.com/products/collar-de-libelula-7</t>
         </is>
       </c>
       <c r="N714" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.47-PM-1.jpg?v=1745622227</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.42-PM-1.jpg?v=1745622227</t>
         </is>
       </c>
       <c r="O714" s="2" t="n">
@@ -43348,11 +43348,11 @@
     </row>
     <row r="715">
       <c r="A715" s="2" t="n">
-        <v>8980471578845</v>
+        <v>8980471251165</v>
       </c>
       <c r="B715" s="2" t="inlineStr">
         <is>
-          <t>Collar de Libélula</t>
+          <t>Collar de Mariquita</t>
         </is>
       </c>
       <c r="C715" s="2" t="inlineStr">
@@ -43391,12 +43391,12 @@
       </c>
       <c r="M715" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-de-libelula-7</t>
+          <t>https://www.gavajoyeria.com/products/collar-de-mariquita-3</t>
         </is>
       </c>
       <c r="N715" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.42-PM-1.jpg?v=1745622227</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.12.35-PM.jpg?v=1745622225</t>
         </is>
       </c>
       <c r="O715" s="2" t="n">
@@ -43406,11 +43406,11 @@
     </row>
     <row r="716">
       <c r="A716" s="2" t="n">
-        <v>8980471251165</v>
+        <v>8980471120093</v>
       </c>
       <c r="B716" s="2" t="inlineStr">
         <is>
-          <t>Collar de Mariquita</t>
+          <t>Collar de Escarabajo</t>
         </is>
       </c>
       <c r="C716" s="2" t="inlineStr">
@@ -43449,12 +43449,12 @@
       </c>
       <c r="M716" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-de-mariquita-3</t>
+          <t>https://www.gavajoyeria.com/products/collar-de-escarabajo</t>
         </is>
       </c>
       <c r="N716" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.12.35-PM.jpg?v=1745622225</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.47-PM-2.jpg?v=1745622225</t>
         </is>
       </c>
       <c r="O716" s="2" t="n">
@@ -43464,11 +43464,11 @@
     </row>
     <row r="717">
       <c r="A717" s="2" t="n">
-        <v>8980471120093</v>
+        <v>9684200620253</v>
       </c>
       <c r="B717" s="2" t="inlineStr">
         <is>
-          <t>Collar de Escarabajo</t>
+          <t>Collar en perla con dije de rodio con maxi aretes</t>
         </is>
       </c>
       <c r="C717" s="2" t="inlineStr">
@@ -43482,7 +43482,7 @@
         </is>
       </c>
       <c r="E717" s="3" t="n">
-        <v>79000</v>
+        <v>76000</v>
       </c>
       <c r="F717" s="3" t="n"/>
       <c r="G717" s="3" t="n"/>
@@ -43507,26 +43507,30 @@
       </c>
       <c r="M717" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-de-escarabajo</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-rodio-copia-1</t>
         </is>
       </c>
       <c r="N717" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.47-PM-2.jpg?v=1745622225</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6264.jpg?v=1790038922</t>
         </is>
       </c>
       <c r="O717" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P717" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P717" s="2" t="inlineStr">
+        <is>
+          <t>Elegancia y delicadeza en una sola pieza. Nuestros collares de perlas con dije son el complemento perfecto para darle un toque sofisticado y femenino a cualquier look. MATERIAL Covergold con doble baño de rodio CUIDA TUS ACCESORIOS ✨ Para conservar su brillo y alargar su vida útil, ten en cuenta estos cuidados: • Evita el contacto con perfumes, sprays y productos químicos fuertes. • Guarda cada ac</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" s="2" t="n">
-        <v>9684200620253</v>
+        <v>9684182204637</v>
       </c>
       <c r="B718" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije de rodio con maxi aretes</t>
+          <t>Collar en perla con dije corazon en nacar</t>
         </is>
       </c>
       <c r="C718" s="2" t="inlineStr">
@@ -43565,12 +43569,12 @@
       </c>
       <c r="M718" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-rodio-copia-1</t>
+          <t>https://www.gavajoyeria.com/products/set-de-collar-en-perla-con-dije-de-cruz-con-perlas-copia</t>
         </is>
       </c>
       <c r="N718" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6264.jpg?v=1790038922</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6247.jpg?v=1790038922</t>
         </is>
       </c>
       <c r="O718" s="2" t="n">
@@ -43584,11 +43588,11 @@
     </row>
     <row r="719">
       <c r="A719" s="2" t="n">
-        <v>9684182204637</v>
+        <v>9684192297181</v>
       </c>
       <c r="B719" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije corazon en nacar</t>
+          <t>Collar en perla con dije Religioso</t>
         </is>
       </c>
       <c r="C719" s="2" t="inlineStr">
@@ -43602,7 +43606,7 @@
         </is>
       </c>
       <c r="E719" s="3" t="n">
-        <v>76000</v>
+        <v>74000</v>
       </c>
       <c r="F719" s="3" t="n"/>
       <c r="G719" s="3" t="n"/>
@@ -43627,12 +43631,12 @@
       </c>
       <c r="M719" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/set-de-collar-en-perla-con-dije-de-cruz-con-perlas-copia</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-religioso-copia</t>
         </is>
       </c>
       <c r="N719" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6247.jpg?v=1790038922</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6255.jpg?v=1790038922</t>
         </is>
       </c>
       <c r="O719" s="2" t="n">
@@ -43646,11 +43650,11 @@
     </row>
     <row r="720">
       <c r="A720" s="2" t="n">
-        <v>9684192297181</v>
+        <v>9684110016733</v>
       </c>
       <c r="B720" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije Religioso</t>
+          <t>Collar en perla con dije en rodio virgen de guadalupe</t>
         </is>
       </c>
       <c r="C720" s="2" t="inlineStr">
@@ -43689,12 +43693,12 @@
       </c>
       <c r="M720" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-religioso-copia</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-en-rodio-copia-4</t>
         </is>
       </c>
       <c r="N720" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6255.jpg?v=1790038922</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6219.jpg?v=1790037164</t>
         </is>
       </c>
       <c r="O720" s="2" t="n">
@@ -43708,11 +43712,11 @@
     </row>
     <row r="721">
       <c r="A721" s="2" t="n">
-        <v>9684110016733</v>
+        <v>10192832495837</v>
       </c>
       <c r="B721" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije en rodio virgen de guadalupe</t>
+          <t>Collar en perla con dije en rodio</t>
         </is>
       </c>
       <c r="C721" s="2" t="inlineStr">
@@ -43726,7 +43730,7 @@
         </is>
       </c>
       <c r="E721" s="3" t="n">
-        <v>74000</v>
+        <v>72000</v>
       </c>
       <c r="F721" s="3" t="n"/>
       <c r="G721" s="3" t="n"/>
@@ -43751,12 +43755,12 @@
       </c>
       <c r="M721" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-en-rodio-copia-4</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-nacar-copia</t>
         </is>
       </c>
       <c r="N721" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6219.jpg?v=1790037164</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6291.jpg?v=1790041671</t>
         </is>
       </c>
       <c r="O721" s="2" t="n">
@@ -43770,11 +43774,11 @@
     </row>
     <row r="722">
       <c r="A722" s="2" t="n">
-        <v>10192832495837</v>
+        <v>9684204388573</v>
       </c>
       <c r="B722" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije en rodio</t>
+          <t>Collar en perla con dije en cruz con perlas</t>
         </is>
       </c>
       <c r="C722" s="2" t="inlineStr">
@@ -43813,12 +43817,12 @@
       </c>
       <c r="M722" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-nacar-copia</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-corazon-copia</t>
         </is>
       </c>
       <c r="N722" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6291.jpg?v=1790041671</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6275.jpg?v=1790041671</t>
         </is>
       </c>
       <c r="O722" s="2" t="n">
@@ -43832,11 +43836,11 @@
     </row>
     <row r="723">
       <c r="A723" s="2" t="n">
-        <v>9684204388573</v>
+        <v>9684120633565</v>
       </c>
       <c r="B723" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije en cruz con perlas</t>
+          <t>Collar en perla con dije en rodio</t>
         </is>
       </c>
       <c r="C723" s="2" t="inlineStr">
@@ -43875,12 +43879,12 @@
       </c>
       <c r="M723" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-corazon-copia</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-en-rodio-copia-6</t>
         </is>
       </c>
       <c r="N723" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6275.jpg?v=1790041671</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6227.jpg?v=1790037164</t>
         </is>
       </c>
       <c r="O723" s="2" t="n">
@@ -43894,7 +43898,7 @@
     </row>
     <row r="724">
       <c r="A724" s="2" t="n">
-        <v>9684120633565</v>
+        <v>9684106248413</v>
       </c>
       <c r="B724" s="2" t="inlineStr">
         <is>
@@ -43937,12 +43941,12 @@
       </c>
       <c r="M724" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-en-rodio-copia-6</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-en-rodio-copia</t>
         </is>
       </c>
       <c r="N724" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6227.jpg?v=1790037164</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6211_43d0b6cb-ee56-476c-8e1e-7aa5a9aa5453.jpg?v=1790037164</t>
         </is>
       </c>
       <c r="O724" s="2" t="n">
@@ -43956,11 +43960,11 @@
     </row>
     <row r="725">
       <c r="A725" s="2" t="n">
-        <v>9684106248413</v>
+        <v>9684076363997</v>
       </c>
       <c r="B725" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije en rodio</t>
+          <t>Collar en perla con dije de tres cirulos</t>
         </is>
       </c>
       <c r="C725" s="2" t="inlineStr">
@@ -43999,12 +44003,12 @@
       </c>
       <c r="M725" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-en-rodio-copia</t>
+          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-copia</t>
         </is>
       </c>
       <c r="N725" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6211_43d0b6cb-ee56-476c-8e1e-7aa5a9aa5453.jpg?v=1790037164</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6203.jpg?v=1790037164</t>
         </is>
       </c>
       <c r="O725" s="2" t="n">
@@ -44018,11 +44022,11 @@
     </row>
     <row r="726">
       <c r="A726" s="2" t="n">
-        <v>9684076363997</v>
+        <v>8980463419613</v>
       </c>
       <c r="B726" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije de tres cirulos</t>
+          <t>A42</t>
         </is>
       </c>
       <c r="C726" s="2" t="inlineStr">
@@ -44036,7 +44040,7 @@
         </is>
       </c>
       <c r="E726" s="3" t="n">
-        <v>72000</v>
+        <v>67000</v>
       </c>
       <c r="F726" s="3" t="n"/>
       <c r="G726" s="3" t="n"/>
@@ -44061,30 +44065,26 @@
       </c>
       <c r="M726" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-copia</t>
+          <t>https://www.gavajoyeria.com/products/a42-4</t>
         </is>
       </c>
       <c r="N726" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6203.jpg?v=1790037164</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-04-21-at-4.03.34-PM.jpg?v=1745622201</t>
         </is>
       </c>
       <c r="O726" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P726" s="2" t="inlineStr">
-        <is>
-          <t>Elegancia y delicadeza en una sola pieza. Nuestros collares de perlas con dije son el complemento perfecto para darle un toque sofisticado y femenino a cualquier look. MATERIAL Covergold con doble baño de rodio CUIDA TUS ACCESORIOS ✨ Para conservar su brillo y alargar su vida útil, ten en cuenta estos cuidados: • Evita el contacto con perfumes, sprays y productos químicos fuertes. • Guarda cada ac</t>
-        </is>
-      </c>
+      <c r="P726" s="2" t="inlineStr"/>
     </row>
     <row r="727">
       <c r="A727" s="2" t="n">
-        <v>8980463419613</v>
+        <v>8980472004829</v>
       </c>
       <c r="B727" s="2" t="inlineStr">
         <is>
-          <t>A42</t>
+          <t>Choker de Mariquita</t>
         </is>
       </c>
       <c r="C727" s="2" t="inlineStr">
@@ -44098,7 +44098,7 @@
         </is>
       </c>
       <c r="E727" s="3" t="n">
-        <v>67000</v>
+        <v>66000</v>
       </c>
       <c r="F727" s="3" t="n"/>
       <c r="G727" s="3" t="n"/>
@@ -44123,26 +44123,26 @@
       </c>
       <c r="M727" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/a42-4</t>
+          <t>https://www.gavajoyeria.com/products/choker-de-mariquita</t>
         </is>
       </c>
       <c r="N727" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-04-21-at-4.03.34-PM.jpg?v=1745622201</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.12.39-PM.jpg?v=1745622229</t>
         </is>
       </c>
       <c r="O727" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P727" s="2" t="inlineStr"/>
     </row>
     <row r="728">
       <c r="A728" s="2" t="n">
-        <v>8980472004829</v>
+        <v>8980472365277</v>
       </c>
       <c r="B728" s="2" t="inlineStr">
         <is>
-          <t>Choker de Mariquita</t>
+          <t>Choker de Escarabajo</t>
         </is>
       </c>
       <c r="C728" s="2" t="inlineStr">
@@ -44181,26 +44181,26 @@
       </c>
       <c r="M728" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/choker-de-mariquita</t>
+          <t>https://www.gavajoyeria.com/products/choker-de-escarabajo</t>
         </is>
       </c>
       <c r="N728" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.12.39-PM.jpg?v=1745622229</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-14-at-6.04.09-PM.jpg?v=1745622231</t>
         </is>
       </c>
       <c r="O728" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P728" s="2" t="inlineStr"/>
     </row>
     <row r="729">
       <c r="A729" s="2" t="n">
-        <v>8980472365277</v>
+        <v>8980472529117</v>
       </c>
       <c r="B729" s="2" t="inlineStr">
         <is>
-          <t>Choker de Escarabajo</t>
+          <t>Collar de Escarabajo</t>
         </is>
       </c>
       <c r="C729" s="2" t="inlineStr">
@@ -44239,12 +44239,12 @@
       </c>
       <c r="M729" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/choker-de-escarabajo</t>
+          <t>https://www.gavajoyeria.com/products/colla-de-escarabajo</t>
         </is>
       </c>
       <c r="N729" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-14-at-6.04.09-PM.jpg?v=1745622231</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.50-PM.jpg?v=1745622231</t>
         </is>
       </c>
       <c r="O729" s="2" t="n">
@@ -44254,11 +44254,11 @@
     </row>
     <row r="730">
       <c r="A730" s="2" t="n">
-        <v>8980472529117</v>
+        <v>9684109066461</v>
       </c>
       <c r="B730" s="2" t="inlineStr">
         <is>
-          <t>Collar de Escarabajo</t>
+          <t>Collar en perla con dije en rodio</t>
         </is>
       </c>
       <c r="C730" s="2" t="inlineStr">
@@ -44272,7 +44272,7 @@
         </is>
       </c>
       <c r="E730" s="3" t="n">
-        <v>66000</v>
+        <v>65000</v>
       </c>
       <c r="F730" s="3" t="n"/>
       <c r="G730" s="3" t="n"/>
@@ -44297,26 +44297,30 @@
       </c>
       <c r="M730" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/colla-de-escarabajo</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-en-rodio-copia-3</t>
         </is>
       </c>
       <c r="N730" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.50-PM.jpg?v=1745622231</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6218.jpg?v=1790037164</t>
         </is>
       </c>
       <c r="O730" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P730" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P730" s="2" t="inlineStr">
+        <is>
+          <t>Elegancia y delicadeza en una sola pieza. Nuestros collares de perlas con dije son el complemento perfecto para darle un toque sofisticado y femenino a cualquier look. MATERIAL Covergold con doble baño de rodio CUIDA TUS ACCESORIOS ✨ Para conservar su brillo y alargar su vida útil, ten en cuenta estos cuidados: • Evita el contacto con perfumes, sprays y productos químicos fuertes. • Guarda cada ac</t>
+        </is>
+      </c>
     </row>
     <row r="731">
       <c r="A731" s="2" t="n">
-        <v>9684109066461</v>
+        <v>8980472234205</v>
       </c>
       <c r="B731" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije en rodio</t>
+          <t>Collar de Libélula</t>
         </is>
       </c>
       <c r="C731" s="2" t="inlineStr">
@@ -44330,7 +44334,7 @@
         </is>
       </c>
       <c r="E731" s="3" t="n">
-        <v>65000</v>
+        <v>63000</v>
       </c>
       <c r="F731" s="3" t="n"/>
       <c r="G731" s="3" t="n"/>
@@ -44355,30 +44359,26 @@
       </c>
       <c r="M731" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-en-rodio-copia-3</t>
+          <t>https://www.gavajoyeria.com/products/collar-de-libelula</t>
         </is>
       </c>
       <c r="N731" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6218.jpg?v=1790037164</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.12.29-PM-1-1.jpg?v=1745622230</t>
         </is>
       </c>
       <c r="O731" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P731" s="2" t="inlineStr">
-        <is>
-          <t>Elegancia y delicadeza en una sola pieza. Nuestros collares de perlas con dije son el complemento perfecto para darle un toque sofisticado y femenino a cualquier look. MATERIAL Covergold con doble baño de rodio CUIDA TUS ACCESORIOS ✨ Para conservar su brillo y alargar su vida útil, ten en cuenta estos cuidados: • Evita el contacto con perfumes, sprays y productos químicos fuertes. • Guarda cada ac</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="P731" s="2" t="inlineStr"/>
     </row>
     <row r="732">
       <c r="A732" s="2" t="n">
-        <v>8980472234205</v>
+        <v>8980493697245</v>
       </c>
       <c r="B732" s="2" t="inlineStr">
         <is>
-          <t>Collar de Libélula</t>
+          <t>Collar Con dijes en piedra</t>
         </is>
       </c>
       <c r="C732" s="2" t="inlineStr">
@@ -44392,7 +44392,7 @@
         </is>
       </c>
       <c r="E732" s="3" t="n">
-        <v>63000</v>
+        <v>61000</v>
       </c>
       <c r="F732" s="3" t="n"/>
       <c r="G732" s="3" t="n"/>
@@ -44417,22 +44417,22 @@
       </c>
       <c r="M732" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-de-libelula</t>
+          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-5</t>
         </is>
       </c>
       <c r="N732" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.12.29-PM-1-1.jpg?v=1745622230</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.33-AM-3.jpg?v=1745622298</t>
         </is>
       </c>
       <c r="O732" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P732" s="2" t="inlineStr"/>
     </row>
     <row r="733">
       <c r="A733" s="2" t="n">
-        <v>8980493697245</v>
+        <v>8980493041885</v>
       </c>
       <c r="B733" s="2" t="inlineStr">
         <is>
@@ -44475,12 +44475,12 @@
       </c>
       <c r="M733" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-5</t>
+          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-10</t>
         </is>
       </c>
       <c r="N733" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.33-AM-3.jpg?v=1745622298</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.49-AM.jpg?v=1745622296</t>
         </is>
       </c>
       <c r="O733" s="2" t="n">
@@ -44490,11 +44490,11 @@
     </row>
     <row r="734">
       <c r="A734" s="2" t="n">
-        <v>8980493041885</v>
+        <v>9684196196573</v>
       </c>
       <c r="B734" s="2" t="inlineStr">
         <is>
-          <t>Collar Con dijes en piedra</t>
+          <t>Collar en perla con dije de rodio</t>
         </is>
       </c>
       <c r="C734" s="2" t="inlineStr">
@@ -44508,7 +44508,7 @@
         </is>
       </c>
       <c r="E734" s="3" t="n">
-        <v>61000</v>
+        <v>59000</v>
       </c>
       <c r="F734" s="3" t="n"/>
       <c r="G734" s="3" t="n"/>
@@ -44533,26 +44533,30 @@
       </c>
       <c r="M734" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-10</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-flores-copia</t>
         </is>
       </c>
       <c r="N734" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.49-AM.jpg?v=1745622296</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6260.jpg?v=1790038922</t>
         </is>
       </c>
       <c r="O734" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P734" s="2" t="inlineStr"/>
+      <c r="P734" s="2" t="inlineStr">
+        <is>
+          <t>Elegancia y delicadeza en una sola pieza. Nuestros collares de perlas con dije son el complemento perfecto para darle un toque sofisticado y femenino a cualquier look. MATERIAL Covergold con doble baño de rodio CUIDA TUS ACCESORIOS ✨ Para conservar su brillo y alargar su vida útil, ten en cuenta estos cuidados: • Evita el contacto con perfumes, sprays y productos químicos fuertes. • Guarda cada ac</t>
+        </is>
+      </c>
     </row>
     <row r="735">
       <c r="A735" s="2" t="n">
-        <v>9684196196573</v>
+        <v>8980472430813</v>
       </c>
       <c r="B735" s="2" t="inlineStr">
         <is>
-          <t>Collar en perla con dije de rodio</t>
+          <t>Collar de Escarabajo</t>
         </is>
       </c>
       <c r="C735" s="2" t="inlineStr">
@@ -44566,7 +44570,7 @@
         </is>
       </c>
       <c r="E735" s="3" t="n">
-        <v>59000</v>
+        <v>55000</v>
       </c>
       <c r="F735" s="3" t="n"/>
       <c r="G735" s="3" t="n"/>
@@ -44591,26 +44595,22 @@
       </c>
       <c r="M735" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-perla-con-dije-de-flores-copia</t>
+          <t>https://www.gavajoyeria.com/products/collar-de-escarabajo-8</t>
         </is>
       </c>
       <c r="N735" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/IMG_6260.jpg?v=1790038922</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.50-PM-3.jpg?v=1745622231</t>
         </is>
       </c>
       <c r="O735" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P735" s="2" t="inlineStr">
-        <is>
-          <t>Elegancia y delicadeza en una sola pieza. Nuestros collares de perlas con dije son el complemento perfecto para darle un toque sofisticado y femenino a cualquier look. MATERIAL Covergold con doble baño de rodio CUIDA TUS ACCESORIOS ✨ Para conservar su brillo y alargar su vida útil, ten en cuenta estos cuidados: • Evita el contacto con perfumes, sprays y productos químicos fuertes. • Guarda cada ac</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="P735" s="2" t="inlineStr"/>
     </row>
     <row r="736">
       <c r="A736" s="2" t="n">
-        <v>8980472430813</v>
+        <v>8980472398045</v>
       </c>
       <c r="B736" s="2" t="inlineStr">
         <is>
@@ -44653,26 +44653,26 @@
       </c>
       <c r="M736" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-de-escarabajo-8</t>
+          <t>https://www.gavajoyeria.com/products/collar-de-escarabajo-6</t>
         </is>
       </c>
       <c r="N736" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.50-PM-3.jpg?v=1745622231</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.50-PM-1.jpg?v=1745622231</t>
         </is>
       </c>
       <c r="O736" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P736" s="2" t="inlineStr"/>
     </row>
     <row r="737">
       <c r="A737" s="2" t="n">
-        <v>8980472398045</v>
+        <v>8980471972061</v>
       </c>
       <c r="B737" s="2" t="inlineStr">
         <is>
-          <t>Collar de Escarabajo</t>
+          <t>Collar de Libélula</t>
         </is>
       </c>
       <c r="C737" s="2" t="inlineStr">
@@ -44711,26 +44711,26 @@
       </c>
       <c r="M737" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-de-escarabajo-6</t>
+          <t>https://www.gavajoyeria.com/products/libelula</t>
         </is>
       </c>
       <c r="N737" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.50-PM-1.jpg?v=1745622231</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.12.29-PM-2.jpg?v=1745622229</t>
         </is>
       </c>
       <c r="O737" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P737" s="2" t="inlineStr"/>
     </row>
     <row r="738">
       <c r="A738" s="2" t="n">
-        <v>8980471972061</v>
+        <v>8980471906525</v>
       </c>
       <c r="B738" s="2" t="inlineStr">
         <is>
-          <t>Collar de Libélula</t>
+          <t>Collar de Mariquita</t>
         </is>
       </c>
       <c r="C738" s="2" t="inlineStr">
@@ -44769,12 +44769,12 @@
       </c>
       <c r="M738" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/libelula</t>
+          <t>https://www.gavajoyeria.com/products/collar-de-mariquita-6</t>
         </is>
       </c>
       <c r="N738" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.12.29-PM-2.jpg?v=1745622229</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.52-PM.jpg?v=1745622228</t>
         </is>
       </c>
       <c r="O738" s="2" t="n">
@@ -44784,11 +44784,11 @@
     </row>
     <row r="739">
       <c r="A739" s="2" t="n">
-        <v>8980471906525</v>
+        <v>8980490911965</v>
       </c>
       <c r="B739" s="2" t="inlineStr">
         <is>
-          <t>Collar de Mariquita</t>
+          <t>Collar Con dijes en piedra</t>
         </is>
       </c>
       <c r="C739" s="2" t="inlineStr">
@@ -44802,7 +44802,7 @@
         </is>
       </c>
       <c r="E739" s="3" t="n">
-        <v>55000</v>
+        <v>53000</v>
       </c>
       <c r="F739" s="3" t="n"/>
       <c r="G739" s="3" t="n"/>
@@ -44827,26 +44827,26 @@
       </c>
       <c r="M739" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-de-mariquita-6</t>
+          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-11</t>
         </is>
       </c>
       <c r="N739" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.11.52-PM.jpg?v=1745622228</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.41-AM.jpg?v=1745622289</t>
         </is>
       </c>
       <c r="O739" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P739" s="2" t="inlineStr"/>
     </row>
     <row r="740">
       <c r="A740" s="2" t="n">
-        <v>8980490911965</v>
+        <v>8980491436253</v>
       </c>
       <c r="B740" s="2" t="inlineStr">
         <is>
-          <t>Collar Con dijes en piedra</t>
+          <t>Collar en Coverlgold Rodinado</t>
         </is>
       </c>
       <c r="C740" s="2" t="inlineStr">
@@ -44885,12 +44885,12 @@
       </c>
       <c r="M740" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-11</t>
+          <t>https://www.gavajoyeria.com/products/cadenas-en-coverl-gold-39</t>
         </is>
       </c>
       <c r="N740" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.41-AM.jpg?v=1745622289</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-9.50.12-AM.jpg?v=1745622291</t>
         </is>
       </c>
       <c r="O740" s="2" t="n">
@@ -44900,7 +44900,7 @@
     </row>
     <row r="741">
       <c r="A741" s="2" t="n">
-        <v>8980491436253</v>
+        <v>8980491010269</v>
       </c>
       <c r="B741" s="2" t="inlineStr">
         <is>
@@ -44943,12 +44943,12 @@
       </c>
       <c r="M741" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/cadenas-en-coverl-gold-39</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-coverlgold-rodinado-3</t>
         </is>
       </c>
       <c r="N741" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-9.50.12-AM.jpg?v=1745622291</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-9.37.36-AM.jpg?v=1745622290</t>
         </is>
       </c>
       <c r="O741" s="2" t="n">
@@ -44958,7 +44958,7 @@
     </row>
     <row r="742">
       <c r="A742" s="2" t="n">
-        <v>8980491010269</v>
+        <v>8980492714205</v>
       </c>
       <c r="B742" s="2" t="inlineStr">
         <is>
@@ -44976,7 +44976,7 @@
         </is>
       </c>
       <c r="E742" s="3" t="n">
-        <v>53000</v>
+        <v>50000</v>
       </c>
       <c r="F742" s="3" t="n"/>
       <c r="G742" s="3" t="n"/>
@@ -45001,12 +45001,12 @@
       </c>
       <c r="M742" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-coverlgold-rodinado-3</t>
+          <t>https://www.gavajoyeria.com/products/cadenas-en-coverl-gold-40</t>
         </is>
       </c>
       <c r="N742" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-9.37.36-AM.jpg?v=1745622290</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-9.46.14-AM.jpg?v=1745622295</t>
         </is>
       </c>
       <c r="O742" s="2" t="n">
@@ -45016,7 +45016,7 @@
     </row>
     <row r="743">
       <c r="A743" s="2" t="n">
-        <v>8980492714205</v>
+        <v>8980491829469</v>
       </c>
       <c r="B743" s="2" t="inlineStr">
         <is>
@@ -45059,12 +45059,12 @@
       </c>
       <c r="M743" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/cadenas-en-coverl-gold-40</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-coverlgold-rodinado</t>
         </is>
       </c>
       <c r="N743" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-9.46.14-AM.jpg?v=1745622295</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-9.43.58-AM.jpg?v=1745622292</t>
         </is>
       </c>
       <c r="O743" s="2" t="n">
@@ -45074,7 +45074,7 @@
     </row>
     <row r="744">
       <c r="A744" s="2" t="n">
-        <v>8980491829469</v>
+        <v>8980489732317</v>
       </c>
       <c r="B744" s="2" t="inlineStr">
         <is>
@@ -45117,12 +45117,12 @@
       </c>
       <c r="M744" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-coverlgold-rodinado</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-coverlgold-rodinado-2</t>
         </is>
       </c>
       <c r="N744" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-9.43.58-AM.jpg?v=1745622292</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-9.40.09-AM.jpg?v=1745622286</t>
         </is>
       </c>
       <c r="O744" s="2" t="n">
@@ -45132,11 +45132,11 @@
     </row>
     <row r="745">
       <c r="A745" s="2" t="n">
-        <v>8980489732317</v>
+        <v>8980493893853</v>
       </c>
       <c r="B745" s="2" t="inlineStr">
         <is>
-          <t>Collar en Coverlgold Rodinado</t>
+          <t>Collar Con dijes en piedra</t>
         </is>
       </c>
       <c r="C745" s="2" t="inlineStr">
@@ -45150,7 +45150,7 @@
         </is>
       </c>
       <c r="E745" s="3" t="n">
-        <v>50000</v>
+        <v>49000</v>
       </c>
       <c r="F745" s="3" t="n"/>
       <c r="G745" s="3" t="n"/>
@@ -45175,12 +45175,12 @@
       </c>
       <c r="M745" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-coverlgold-rodinado-2</t>
+          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-9</t>
         </is>
       </c>
       <c r="N745" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-9.40.09-AM.jpg?v=1745622286</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.15-AM-3.jpg?v=1745622298</t>
         </is>
       </c>
       <c r="O745" s="2" t="n">
@@ -45190,7 +45190,7 @@
     </row>
     <row r="746">
       <c r="A746" s="2" t="n">
-        <v>8980493893853</v>
+        <v>8980491862237</v>
       </c>
       <c r="B746" s="2" t="inlineStr">
         <is>
@@ -45208,7 +45208,7 @@
         </is>
       </c>
       <c r="E746" s="3" t="n">
-        <v>49000</v>
+        <v>48000</v>
       </c>
       <c r="F746" s="3" t="n"/>
       <c r="G746" s="3" t="n"/>
@@ -45233,12 +45233,12 @@
       </c>
       <c r="M746" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-9</t>
+          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-3</t>
         </is>
       </c>
       <c r="N746" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.15-AM-3.jpg?v=1745622298</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.49-AM-1.jpg?v=1745622292</t>
         </is>
       </c>
       <c r="O746" s="2" t="n">
@@ -45248,7 +45248,7 @@
     </row>
     <row r="747">
       <c r="A747" s="2" t="n">
-        <v>8980491862237</v>
+        <v>8980492648669</v>
       </c>
       <c r="B747" s="2" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         </is>
       </c>
       <c r="E747" s="3" t="n">
-        <v>48000</v>
+        <v>47000</v>
       </c>
       <c r="F747" s="3" t="n"/>
       <c r="G747" s="3" t="n"/>
@@ -45291,12 +45291,12 @@
       </c>
       <c r="M747" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-3</t>
+          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra</t>
         </is>
       </c>
       <c r="N747" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.49-AM-1.jpg?v=1745622292</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.49-AM-3.jpg?v=1745622295</t>
         </is>
       </c>
       <c r="O747" s="2" t="n">
@@ -45306,7 +45306,7 @@
     </row>
     <row r="748">
       <c r="A748" s="2" t="n">
-        <v>8980492648669</v>
+        <v>8980492779741</v>
       </c>
       <c r="B748" s="2" t="inlineStr">
         <is>
@@ -45349,12 +45349,12 @@
       </c>
       <c r="M748" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra</t>
+          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-13</t>
         </is>
       </c>
       <c r="N748" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.49-AM-3.jpg?v=1745622295</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.34-AM.jpg?v=1745622295</t>
         </is>
       </c>
       <c r="O748" s="2" t="n">
@@ -45364,7 +45364,7 @@
     </row>
     <row r="749">
       <c r="A749" s="2" t="n">
-        <v>8980492779741</v>
+        <v>8980492910813</v>
       </c>
       <c r="B749" s="2" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         </is>
       </c>
       <c r="E749" s="3" t="n">
-        <v>47000</v>
+        <v>46000</v>
       </c>
       <c r="F749" s="3" t="n"/>
       <c r="G749" s="3" t="n"/>
@@ -45407,12 +45407,12 @@
       </c>
       <c r="M749" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-13</t>
+          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-6</t>
         </is>
       </c>
       <c r="N749" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.34-AM.jpg?v=1745622295</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.33-AM-2.jpg?v=1745622295</t>
         </is>
       </c>
       <c r="O749" s="2" t="n">
@@ -45422,7 +45422,7 @@
     </row>
     <row r="750">
       <c r="A750" s="2" t="n">
-        <v>8980492910813</v>
+        <v>8980492419293</v>
       </c>
       <c r="B750" s="2" t="inlineStr">
         <is>
@@ -45465,12 +45465,12 @@
       </c>
       <c r="M750" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-6</t>
+          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-4</t>
         </is>
       </c>
       <c r="N750" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.33-AM-2.jpg?v=1745622295</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.38-AM.jpg?v=1745622294</t>
         </is>
       </c>
       <c r="O750" s="2" t="n">
@@ -45480,7 +45480,7 @@
     </row>
     <row r="751">
       <c r="A751" s="2" t="n">
-        <v>8980492419293</v>
+        <v>8980494057693</v>
       </c>
       <c r="B751" s="2" t="inlineStr">
         <is>
@@ -45498,7 +45498,7 @@
         </is>
       </c>
       <c r="E751" s="3" t="n">
-        <v>46000</v>
+        <v>43000</v>
       </c>
       <c r="F751" s="3" t="n"/>
       <c r="G751" s="3" t="n"/>
@@ -45523,12 +45523,12 @@
       </c>
       <c r="M751" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-4</t>
+          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-14</t>
         </is>
       </c>
       <c r="N751" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.38-AM.jpg?v=1745622294</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.33-AM.jpg?v=1745622299</t>
         </is>
       </c>
       <c r="O751" s="2" t="n">
@@ -45538,7 +45538,7 @@
     </row>
     <row r="752">
       <c r="A752" s="2" t="n">
-        <v>8980494057693</v>
+        <v>8980491075805</v>
       </c>
       <c r="B752" s="2" t="inlineStr">
         <is>
@@ -45581,12 +45581,12 @@
       </c>
       <c r="M752" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-14</t>
+          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-15</t>
         </is>
       </c>
       <c r="N752" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.33-AM.jpg?v=1745622299</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.18-AM-1.jpg?v=1745622290</t>
         </is>
       </c>
       <c r="O752" s="2" t="n">
@@ -45596,11 +45596,11 @@
     </row>
     <row r="753">
       <c r="A753" s="2" t="n">
-        <v>8980491075805</v>
+        <v>8980480229597</v>
       </c>
       <c r="B753" s="2" t="inlineStr">
         <is>
-          <t>Collar Con dijes en piedra</t>
+          <t>Collar en Covergold Rodinado</t>
         </is>
       </c>
       <c r="C753" s="2" t="inlineStr">
@@ -45639,12 +45639,12 @@
       </c>
       <c r="M753" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-15</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-covergold-rodinado-9</t>
         </is>
       </c>
       <c r="N753" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.18-AM-1.jpg?v=1745622290</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-11-at-12.11.48-PM.jpg?v=1745622256</t>
         </is>
       </c>
       <c r="O753" s="2" t="n">
@@ -45654,11 +45654,11 @@
     </row>
     <row r="754">
       <c r="A754" s="2" t="n">
-        <v>8980480229597</v>
+        <v>8980463288541</v>
       </c>
       <c r="B754" s="2" t="inlineStr">
         <is>
-          <t>Collar en Covergold Rodinado</t>
+          <t>A41</t>
         </is>
       </c>
       <c r="C754" s="2" t="inlineStr">
@@ -45672,7 +45672,7 @@
         </is>
       </c>
       <c r="E754" s="3" t="n">
-        <v>43000</v>
+        <v>41000</v>
       </c>
       <c r="F754" s="3" t="n"/>
       <c r="G754" s="3" t="n"/>
@@ -45697,12 +45697,12 @@
       </c>
       <c r="M754" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-covergold-rodinado-9</t>
+          <t>https://www.gavajoyeria.com/products/a41-3</t>
         </is>
       </c>
       <c r="N754" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-11-at-12.11.48-PM.jpg?v=1745622256</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-04-21-at-4.17.41-PM.jpg?v=1745622200</t>
         </is>
       </c>
       <c r="O754" s="2" t="n">
@@ -45712,11 +45712,11 @@
     </row>
     <row r="755">
       <c r="A755" s="2" t="n">
-        <v>8980463288541</v>
+        <v>8980490158301</v>
       </c>
       <c r="B755" s="2" t="inlineStr">
         <is>
-          <t>A41</t>
+          <t>Collar en Covergold Rodinado</t>
         </is>
       </c>
       <c r="C755" s="2" t="inlineStr">
@@ -45730,7 +45730,7 @@
         </is>
       </c>
       <c r="E755" s="3" t="n">
-        <v>41000</v>
+        <v>37000</v>
       </c>
       <c r="F755" s="3" t="n"/>
       <c r="G755" s="3" t="n"/>
@@ -45755,12 +45755,12 @@
       </c>
       <c r="M755" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/a41-3</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-covergold-rodinado-14</t>
         </is>
       </c>
       <c r="N755" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-04-21-at-4.17.41-PM.jpg?v=1745622200</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-05-at-5.29.06-PM.jpg?v=1745622287</t>
         </is>
       </c>
       <c r="O755" s="2" t="n">
@@ -45770,7 +45770,7 @@
     </row>
     <row r="756">
       <c r="A756" s="2" t="n">
-        <v>8980490158301</v>
+        <v>8980489765085</v>
       </c>
       <c r="B756" s="2" t="inlineStr">
         <is>
@@ -45813,12 +45813,12 @@
       </c>
       <c r="M756" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-covergold-rodinado-14</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-covergold-rodinado-13</t>
         </is>
       </c>
       <c r="N756" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-05-at-5.29.06-PM.jpg?v=1745622287</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-6.25.28-AM-1.jpg?v=1745622286</t>
         </is>
       </c>
       <c r="O756" s="2" t="n">
@@ -45828,11 +45828,11 @@
     </row>
     <row r="757">
       <c r="A757" s="2" t="n">
-        <v>8980489765085</v>
+        <v>8980492189917</v>
       </c>
       <c r="B757" s="2" t="inlineStr">
         <is>
-          <t>Collar en Covergold Rodinado</t>
+          <t>Collar Con dijes en piedra</t>
         </is>
       </c>
       <c r="C757" s="2" t="inlineStr">
@@ -45846,7 +45846,7 @@
         </is>
       </c>
       <c r="E757" s="3" t="n">
-        <v>37000</v>
+        <v>35000</v>
       </c>
       <c r="F757" s="3" t="n"/>
       <c r="G757" s="3" t="n"/>
@@ -45871,12 +45871,12 @@
       </c>
       <c r="M757" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-covergold-rodinado-13</t>
+          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-12</t>
         </is>
       </c>
       <c r="N757" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-6.25.28-AM-1.jpg?v=1745622286</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.36-AM.jpg?v=1745622293</t>
         </is>
       </c>
       <c r="O757" s="2" t="n">
@@ -45886,11 +45886,11 @@
     </row>
     <row r="758">
       <c r="A758" s="2" t="n">
-        <v>8980492189917</v>
+        <v>8980479017181</v>
       </c>
       <c r="B758" s="2" t="inlineStr">
         <is>
-          <t>Collar Con dijes en piedra</t>
+          <t>Collar en Covergold Rodinado</t>
         </is>
       </c>
       <c r="C758" s="2" t="inlineStr">
@@ -45904,7 +45904,7 @@
         </is>
       </c>
       <c r="E758" s="3" t="n">
-        <v>35000</v>
+        <v>32000</v>
       </c>
       <c r="F758" s="3" t="n"/>
       <c r="G758" s="3" t="n"/>
@@ -45929,12 +45929,12 @@
       </c>
       <c r="M758" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-12</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-covergold-rodinado-8</t>
         </is>
       </c>
       <c r="N758" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.36-AM.jpg?v=1745622293</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-11-at-12.05.58-PM.jpg?v=1745622252</t>
         </is>
       </c>
       <c r="O758" s="2" t="n">
@@ -45944,11 +45944,11 @@
     </row>
     <row r="759">
       <c r="A759" s="2" t="n">
-        <v>8980479017181</v>
+        <v>8980493172957</v>
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>Collar en Covergold Rodinado</t>
+          <t>Collar Con dijes en piedra cada una</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -45962,7 +45962,7 @@
         </is>
       </c>
       <c r="E759" s="3" t="n">
-        <v>32000</v>
+        <v>31000</v>
       </c>
       <c r="F759" s="3" t="n"/>
       <c r="G759" s="3" t="n"/>
@@ -45987,12 +45987,12 @@
       </c>
       <c r="M759" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-covergold-rodinado-8</t>
+          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-cada-una-2</t>
         </is>
       </c>
       <c r="N759" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-11-at-12.05.58-PM.jpg?v=1745622252</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.31-AM.jpg?v=1745622296</t>
         </is>
       </c>
       <c r="O759" s="2" t="n">
@@ -46002,11 +46002,11 @@
     </row>
     <row r="760">
       <c r="A760" s="2" t="n">
-        <v>8980493172957</v>
+        <v>8980478820573</v>
       </c>
       <c r="B760" s="2" t="inlineStr">
         <is>
-          <t>Collar Con dijes en piedra cada una</t>
+          <t>Collar en Covergold Rodinado</t>
         </is>
       </c>
       <c r="C760" s="2" t="inlineStr">
@@ -46020,7 +46020,7 @@
         </is>
       </c>
       <c r="E760" s="3" t="n">
-        <v>31000</v>
+        <v>27000</v>
       </c>
       <c r="F760" s="3" t="n"/>
       <c r="G760" s="3" t="n"/>
@@ -46045,12 +46045,12 @@
       </c>
       <c r="M760" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-con-dijes-en-piedra-cada-una-2</t>
+          <t>https://www.gavajoyeria.com/products/collar-en-covergold-rodinado-3</t>
         </is>
       </c>
       <c r="N760" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-11.32.31-AM.jpg?v=1745622296</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-11-at-11.40.30-AM.jpg?v=1745622252</t>
         </is>
       </c>
       <c r="O760" s="2" t="n">
@@ -46060,11 +46060,11 @@
     </row>
     <row r="761">
       <c r="A761" s="2" t="n">
-        <v>8980478820573</v>
+        <v>8980489830621</v>
       </c>
       <c r="B761" s="2" t="inlineStr">
         <is>
-          <t>Collar en Covergold Rodinado</t>
+          <t>Set en Covergold Rodinado Collar</t>
         </is>
       </c>
       <c r="C761" s="2" t="inlineStr">
@@ -46078,7 +46078,7 @@
         </is>
       </c>
       <c r="E761" s="3" t="n">
-        <v>27000</v>
+        <v>25500</v>
       </c>
       <c r="F761" s="3" t="n"/>
       <c r="G761" s="3" t="n"/>
@@ -46103,40 +46103,44 @@
       </c>
       <c r="M761" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/collar-en-covergold-rodinado-3</t>
+          <t>https://www.gavajoyeria.com/products/set-en-covergold-rodinado-collar-7</t>
         </is>
       </c>
       <c r="N761" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-11-at-11.40.30-AM.jpg?v=1745622252</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-6.22.32-AM-3.jpg?v=1745622286</t>
         </is>
       </c>
       <c r="O761" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P761" s="2" t="inlineStr"/>
+      <c r="P761" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
     </row>
     <row r="762">
       <c r="A762" s="2" t="n">
-        <v>8980489830621</v>
+        <v>8980489797853</v>
       </c>
       <c r="B762" s="2" t="inlineStr">
         <is>
-          <t>Set en Covergold Rodinado Collar</t>
+          <t>Earcuff en Covergold Rodinado</t>
         </is>
       </c>
       <c r="C762" s="2" t="inlineStr">
         <is>
-          <t>Choker</t>
+          <t>Earcuff</t>
         </is>
       </c>
       <c r="D762" s="2" t="inlineStr">
         <is>
-          <t>Collares</t>
+          <t>Earcuff</t>
         </is>
       </c>
       <c r="E762" s="3" t="n">
-        <v>25500</v>
+        <v>8000</v>
       </c>
       <c r="F762" s="3" t="n"/>
       <c r="G762" s="3" t="n"/>
@@ -46151,7 +46155,7 @@
       </c>
       <c r="K762" s="2" t="inlineStr">
         <is>
-          <t>choker</t>
+          <t>earcuff</t>
         </is>
       </c>
       <c r="L762" s="2" t="inlineStr">
@@ -46161,26 +46165,22 @@
       </c>
       <c r="M762" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/set-en-covergold-rodinado-collar-7</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-38</t>
         </is>
       </c>
       <c r="N762" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-6.22.32-AM-3.jpg?v=1745622286</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-05-at-3.29.23-PM.jpg?v=1745622286</t>
         </is>
       </c>
       <c r="O762" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P762" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+      <c r="P762" s="2" t="inlineStr"/>
     </row>
     <row r="763">
       <c r="A763" s="2" t="n">
-        <v>8980489797853</v>
+        <v>8980489240797</v>
       </c>
       <c r="B763" s="2" t="inlineStr">
         <is>
@@ -46223,12 +46223,12 @@
       </c>
       <c r="M763" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-38</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-36</t>
         </is>
       </c>
       <c r="N763" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-05-at-3.29.23-PM.jpg?v=1745622286</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-05-at-3.22.41-PM.jpg?v=1745622285</t>
         </is>
       </c>
       <c r="O763" s="2" t="n">
@@ -46238,7 +46238,7 @@
     </row>
     <row r="764">
       <c r="A764" s="2" t="n">
-        <v>8980489240797</v>
+        <v>8980489142493</v>
       </c>
       <c r="B764" s="2" t="inlineStr">
         <is>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="E764" s="3" t="n">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="F764" s="3" t="n"/>
       <c r="G764" s="3" t="n"/>
@@ -46281,12 +46281,12 @@
       </c>
       <c r="M764" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-36</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-12</t>
         </is>
       </c>
       <c r="N764" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-05-at-3.22.41-PM.jpg?v=1745622285</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.31.02-AM.jpg?v=1745622284</t>
         </is>
       </c>
       <c r="O764" s="2" t="n">
@@ -46296,7 +46296,7 @@
     </row>
     <row r="765">
       <c r="A765" s="2" t="n">
-        <v>8980489142493</v>
+        <v>8980488978653</v>
       </c>
       <c r="B765" s="2" t="inlineStr">
         <is>
@@ -46339,12 +46339,12 @@
       </c>
       <c r="M765" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-12</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-7</t>
         </is>
       </c>
       <c r="N765" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.31.02-AM.jpg?v=1745622284</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.29.35-AM.jpg?v=1745622283</t>
         </is>
       </c>
       <c r="O765" s="2" t="n">
@@ -46354,7 +46354,7 @@
     </row>
     <row r="766">
       <c r="A766" s="2" t="n">
-        <v>8980488978653</v>
+        <v>8980488749277</v>
       </c>
       <c r="B766" s="2" t="inlineStr">
         <is>
@@ -46397,12 +46397,12 @@
       </c>
       <c r="M766" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-7</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-2</t>
         </is>
       </c>
       <c r="N766" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.29.35-AM.jpg?v=1745622283</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.29.05-AM.jpg?v=1745622283</t>
         </is>
       </c>
       <c r="O766" s="2" t="n">
@@ -46412,7 +46412,7 @@
     </row>
     <row r="767">
       <c r="A767" s="2" t="n">
-        <v>8980488749277</v>
+        <v>8980488454365</v>
       </c>
       <c r="B767" s="2" t="inlineStr">
         <is>
@@ -46455,12 +46455,12 @@
       </c>
       <c r="M767" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-2</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-13</t>
         </is>
       </c>
       <c r="N767" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.29.05-AM.jpg?v=1745622283</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.31.13-AM.jpg?v=1745622282</t>
         </is>
       </c>
       <c r="O767" s="2" t="n">
@@ -46470,7 +46470,7 @@
     </row>
     <row r="768">
       <c r="A768" s="2" t="n">
-        <v>8980488454365</v>
+        <v>8980488290525</v>
       </c>
       <c r="B768" s="2" t="inlineStr">
         <is>
@@ -46513,12 +46513,12 @@
       </c>
       <c r="M768" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-13</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-8</t>
         </is>
       </c>
       <c r="N768" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.31.13-AM.jpg?v=1745622282</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.29.53-AM.jpg?v=1745622281</t>
         </is>
       </c>
       <c r="O768" s="2" t="n">
@@ -46528,7 +46528,7 @@
     </row>
     <row r="769">
       <c r="A769" s="2" t="n">
-        <v>8980488290525</v>
+        <v>8980488126685</v>
       </c>
       <c r="B769" s="2" t="inlineStr">
         <is>
@@ -46571,12 +46571,12 @@
       </c>
       <c r="M769" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-8</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-3</t>
         </is>
       </c>
       <c r="N769" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.29.53-AM.jpg?v=1745622281</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.29.11-AM.jpg?v=1745622281</t>
         </is>
       </c>
       <c r="O769" s="2" t="n">
@@ -46586,7 +46586,7 @@
     </row>
     <row r="770">
       <c r="A770" s="2" t="n">
-        <v>8980488126685</v>
+        <v>8980487864541</v>
       </c>
       <c r="B770" s="2" t="inlineStr">
         <is>
@@ -46629,12 +46629,12 @@
       </c>
       <c r="M770" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-3</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-11</t>
         </is>
       </c>
       <c r="N770" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.29.11-AM.jpg?v=1745622281</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.30.55-AM.jpg?v=1745622280</t>
         </is>
       </c>
       <c r="O770" s="2" t="n">
@@ -46644,7 +46644,7 @@
     </row>
     <row r="771">
       <c r="A771" s="2" t="n">
-        <v>8980487864541</v>
+        <v>8980487667933</v>
       </c>
       <c r="B771" s="2" t="inlineStr">
         <is>
@@ -46687,12 +46687,12 @@
       </c>
       <c r="M771" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-11</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-6</t>
         </is>
       </c>
       <c r="N771" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.30.55-AM.jpg?v=1745622280</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.29.29-AM.jpg?v=1745622280</t>
         </is>
       </c>
       <c r="O771" s="2" t="n">
@@ -46702,7 +46702,7 @@
     </row>
     <row r="772">
       <c r="A772" s="2" t="n">
-        <v>8980487667933</v>
+        <v>8980487504093</v>
       </c>
       <c r="B772" s="2" t="inlineStr">
         <is>
@@ -46745,12 +46745,12 @@
       </c>
       <c r="M772" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-6</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado</t>
         </is>
       </c>
       <c r="N772" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.29.29-AM.jpg?v=1745622280</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.04.38-AM.jpg?v=1745622279</t>
         </is>
       </c>
       <c r="O772" s="2" t="n">
@@ -46760,7 +46760,7 @@
     </row>
     <row r="773">
       <c r="A773" s="2" t="n">
-        <v>8980487504093</v>
+        <v>8980486684893</v>
       </c>
       <c r="B773" s="2" t="inlineStr">
         <is>
@@ -46803,12 +46803,12 @@
       </c>
       <c r="M773" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-14</t>
         </is>
       </c>
       <c r="N773" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.04.38-AM.jpg?v=1745622279</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.31.23-AM.jpg?v=1745622276</t>
         </is>
       </c>
       <c r="O773" s="2" t="n">
@@ -46818,7 +46818,7 @@
     </row>
     <row r="774">
       <c r="A774" s="2" t="n">
-        <v>8980486684893</v>
+        <v>8980486521053</v>
       </c>
       <c r="B774" s="2" t="inlineStr">
         <is>
@@ -46861,12 +46861,12 @@
       </c>
       <c r="M774" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-14</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-9</t>
         </is>
       </c>
       <c r="N774" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.31.23-AM.jpg?v=1745622276</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.30.06-AM.jpg?v=1745622276</t>
         </is>
       </c>
       <c r="O774" s="2" t="n">
@@ -46876,7 +46876,7 @@
     </row>
     <row r="775">
       <c r="A775" s="2" t="n">
-        <v>8980486521053</v>
+        <v>8980486324445</v>
       </c>
       <c r="B775" s="2" t="inlineStr">
         <is>
@@ -46919,12 +46919,12 @@
       </c>
       <c r="M775" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-9</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-4</t>
         </is>
       </c>
       <c r="N775" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.30.06-AM.jpg?v=1745622276</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.29.16-AM.jpg?v=1745622275</t>
         </is>
       </c>
       <c r="O775" s="2" t="n">
@@ -46934,7 +46934,7 @@
     </row>
     <row r="776">
       <c r="A776" s="2" t="n">
-        <v>8980486324445</v>
+        <v>8980487799005</v>
       </c>
       <c r="B776" s="2" t="inlineStr">
         <is>
@@ -46977,12 +46977,12 @@
       </c>
       <c r="M776" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-4</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-15</t>
         </is>
       </c>
       <c r="N776" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.29.16-AM.jpg?v=1745622275</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.31.45-AM.jpg?v=1745622280</t>
         </is>
       </c>
       <c r="O776" s="2" t="n">
@@ -46992,7 +46992,7 @@
     </row>
     <row r="777">
       <c r="A777" s="2" t="n">
-        <v>8980487799005</v>
+        <v>8980487635165</v>
       </c>
       <c r="B777" s="2" t="inlineStr">
         <is>
@@ -47035,12 +47035,12 @@
       </c>
       <c r="M777" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-15</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-10</t>
         </is>
       </c>
       <c r="N777" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.31.45-AM.jpg?v=1745622280</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.30.48-AM.jpg?v=1745622279</t>
         </is>
       </c>
       <c r="O777" s="2" t="n">
@@ -47050,7 +47050,7 @@
     </row>
     <row r="778">
       <c r="A778" s="2" t="n">
-        <v>8980487635165</v>
+        <v>8980487471325</v>
       </c>
       <c r="B778" s="2" t="inlineStr">
         <is>
@@ -47093,12 +47093,12 @@
       </c>
       <c r="M778" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-10</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-5</t>
         </is>
       </c>
       <c r="N778" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.30.48-AM.jpg?v=1745622279</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.29.23-AM.jpg?v=1745622279</t>
         </is>
       </c>
       <c r="O778" s="2" t="n">
@@ -47108,11 +47108,11 @@
     </row>
     <row r="779">
       <c r="A779" s="2" t="n">
-        <v>8980487471325</v>
+        <v>8980465156317</v>
       </c>
       <c r="B779" s="2" t="inlineStr">
         <is>
-          <t>Earcuff en Covergold Rodinado</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="C779" s="2" t="inlineStr">
@@ -47151,12 +47151,12 @@
       </c>
       <c r="M779" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-5</t>
+          <t>https://www.gavajoyeria.com/products/a7-6</t>
         </is>
       </c>
       <c r="N779" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.29.23-AM.jpg?v=1745622279</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-06-27-at-3.14.32-PM-2.jpg?v=1745622206</t>
         </is>
       </c>
       <c r="O779" s="2" t="n">
@@ -47166,11 +47166,11 @@
     </row>
     <row r="780">
       <c r="A780" s="2" t="n">
-        <v>8980465156317</v>
+        <v>8980489863389</v>
       </c>
       <c r="B780" s="2" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>Earcuff en Covergold Rodinado</t>
         </is>
       </c>
       <c r="C780" s="2" t="inlineStr">
@@ -47184,7 +47184,7 @@
         </is>
       </c>
       <c r="E780" s="3" t="n">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="F780" s="3" t="n"/>
       <c r="G780" s="3" t="n"/>
@@ -47209,12 +47209,12 @@
       </c>
       <c r="M780" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/a7-6</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-32</t>
         </is>
       </c>
       <c r="N780" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-06-27-at-3.14.32-PM-2.jpg?v=1745622206</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-25-at-4.48.55-PM.jpg?v=1745622286</t>
         </is>
       </c>
       <c r="O780" s="2" t="n">
@@ -47224,7 +47224,7 @@
     </row>
     <row r="781">
       <c r="A781" s="2" t="n">
-        <v>8980489863389</v>
+        <v>8980489699549</v>
       </c>
       <c r="B781" s="2" t="inlineStr">
         <is>
@@ -47267,12 +47267,12 @@
       </c>
       <c r="M781" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-32</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-27</t>
         </is>
       </c>
       <c r="N781" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-25-at-4.48.55-PM.jpg?v=1745622286</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-10.58.15-AM.jpg?v=1745622285</t>
         </is>
       </c>
       <c r="O781" s="2" t="n">
@@ -47282,7 +47282,7 @@
     </row>
     <row r="782">
       <c r="A782" s="2" t="n">
-        <v>8980489699549</v>
+        <v>8980489535709</v>
       </c>
       <c r="B782" s="2" t="inlineStr">
         <is>
@@ -47325,12 +47325,12 @@
       </c>
       <c r="M782" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-27</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-22</t>
         </is>
       </c>
       <c r="N782" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-10.58.15-AM.jpg?v=1745622285</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-10.59.24-AM.jpg?v=1745622285</t>
         </is>
       </c>
       <c r="O782" s="2" t="n">
@@ -47340,7 +47340,7 @@
     </row>
     <row r="783">
       <c r="A783" s="2" t="n">
-        <v>8980489535709</v>
+        <v>8980489371869</v>
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
@@ -47383,12 +47383,12 @@
       </c>
       <c r="M783" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-22</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-17</t>
         </is>
       </c>
       <c r="N783" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-10.59.24-AM.jpg?v=1745622285</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.00.29-AM.jpg?v=1745622285</t>
         </is>
       </c>
       <c r="O783" s="2" t="n">
@@ -47398,7 +47398,7 @@
     </row>
     <row r="784">
       <c r="A784" s="2" t="n">
-        <v>8980489371869</v>
+        <v>8980489011421</v>
       </c>
       <c r="B784" s="2" t="inlineStr">
         <is>
@@ -47441,12 +47441,12 @@
       </c>
       <c r="M784" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-17</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-28</t>
         </is>
       </c>
       <c r="N784" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.00.29-AM.jpg?v=1745622285</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-10.57.55-AM.jpg?v=1745622283</t>
         </is>
       </c>
       <c r="O784" s="2" t="n">
@@ -47456,7 +47456,7 @@
     </row>
     <row r="785">
       <c r="A785" s="2" t="n">
-        <v>8980489011421</v>
+        <v>8980488814813</v>
       </c>
       <c r="B785" s="2" t="inlineStr">
         <is>
@@ -47499,12 +47499,12 @@
       </c>
       <c r="M785" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-28</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-23</t>
         </is>
       </c>
       <c r="N785" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-10.57.55-AM.jpg?v=1745622283</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-10.59.08-AM.jpg?v=1745622283</t>
         </is>
       </c>
       <c r="O785" s="2" t="n">
@@ -47514,7 +47514,7 @@
     </row>
     <row r="786">
       <c r="A786" s="2" t="n">
-        <v>8980488814813</v>
+        <v>8980488618205</v>
       </c>
       <c r="B786" s="2" t="inlineStr">
         <is>
@@ -47557,12 +47557,12 @@
       </c>
       <c r="M786" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-23</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-18</t>
         </is>
       </c>
       <c r="N786" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-10.59.08-AM.jpg?v=1745622283</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.00.21-AM.jpg?v=1745622282</t>
         </is>
       </c>
       <c r="O786" s="2" t="n">
@@ -47572,7 +47572,7 @@
     </row>
     <row r="787">
       <c r="A787" s="2" t="n">
-        <v>8980488618205</v>
+        <v>8980489044189</v>
       </c>
       <c r="B787" s="2" t="inlineStr">
         <is>
@@ -47615,12 +47615,12 @@
       </c>
       <c r="M787" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-18</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-33</t>
         </is>
       </c>
       <c r="N787" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.00.21-AM.jpg?v=1745622282</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-05-at-3.20.26-PM.jpg?v=1745622284</t>
         </is>
       </c>
       <c r="O787" s="2" t="n">
@@ -47630,7 +47630,7 @@
     </row>
     <row r="788">
       <c r="A788" s="2" t="n">
-        <v>8980489044189</v>
+        <v>8980488552669</v>
       </c>
       <c r="B788" s="2" t="inlineStr">
         <is>
@@ -47673,12 +47673,12 @@
       </c>
       <c r="M788" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-33</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-31</t>
         </is>
       </c>
       <c r="N788" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-05-at-3.20.26-PM.jpg?v=1745622284</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-10.56.09-AM.jpg?v=1745622282</t>
         </is>
       </c>
       <c r="O788" s="2" t="n">
@@ -47688,7 +47688,7 @@
     </row>
     <row r="789">
       <c r="A789" s="2" t="n">
-        <v>8980488552669</v>
+        <v>8980488388829</v>
       </c>
       <c r="B789" s="2" t="inlineStr">
         <is>
@@ -47731,12 +47731,12 @@
       </c>
       <c r="M789" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-31</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-26</t>
         </is>
       </c>
       <c r="N789" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-10.56.09-AM.jpg?v=1745622282</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-10.58.25-AM.jpg?v=1745622282</t>
         </is>
       </c>
       <c r="O789" s="2" t="n">
@@ -47746,7 +47746,7 @@
     </row>
     <row r="790">
       <c r="A790" s="2" t="n">
-        <v>8980488388829</v>
+        <v>8980488224989</v>
       </c>
       <c r="B790" s="2" t="inlineStr">
         <is>
@@ -47789,12 +47789,12 @@
       </c>
       <c r="M790" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-26</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-21</t>
         </is>
       </c>
       <c r="N790" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-10.58.25-AM.jpg?v=1745622282</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-10.59.32-AM.jpg?v=1745622281</t>
         </is>
       </c>
       <c r="O790" s="2" t="n">
@@ -47804,7 +47804,7 @@
     </row>
     <row r="791">
       <c r="A791" s="2" t="n">
-        <v>8980488224989</v>
+        <v>8980488061149</v>
       </c>
       <c r="B791" s="2" t="inlineStr">
         <is>
@@ -47847,12 +47847,12 @@
       </c>
       <c r="M791" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-21</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-16</t>
         </is>
       </c>
       <c r="N791" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-10.59.32-AM.jpg?v=1745622281</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.00.36-AM.jpg?v=1745622281</t>
         </is>
       </c>
       <c r="O791" s="2" t="n">
@@ -47862,7 +47862,7 @@
     </row>
     <row r="792">
       <c r="A792" s="2" t="n">
-        <v>8980488061149</v>
+        <v>8980486815965</v>
       </c>
       <c r="B792" s="2" t="inlineStr">
         <is>
@@ -47905,12 +47905,12 @@
       </c>
       <c r="M792" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-16</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-19</t>
         </is>
       </c>
       <c r="N792" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-11.00.36-AM.jpg?v=1745622281</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-10.59.57-AM.jpg?v=1745622277</t>
         </is>
       </c>
       <c r="O792" s="2" t="n">
@@ -47920,7 +47920,7 @@
     </row>
     <row r="793">
       <c r="A793" s="2" t="n">
-        <v>8980486815965</v>
+        <v>8980488323293</v>
       </c>
       <c r="B793" s="2" t="inlineStr">
         <is>
@@ -47963,12 +47963,12 @@
       </c>
       <c r="M793" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-19</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-30</t>
         </is>
       </c>
       <c r="N793" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-10.59.57-AM.jpg?v=1745622277</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-10.57.22-AM.jpg?v=1745622281</t>
         </is>
       </c>
       <c r="O793" s="2" t="n">
@@ -47978,7 +47978,7 @@
     </row>
     <row r="794">
       <c r="A794" s="2" t="n">
-        <v>8980488323293</v>
+        <v>8980488159453</v>
       </c>
       <c r="B794" s="2" t="inlineStr">
         <is>
@@ -48021,12 +48021,12 @@
       </c>
       <c r="M794" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-30</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-25</t>
         </is>
       </c>
       <c r="N794" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-10.57.22-AM.jpg?v=1745622281</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-10.58.49-AM.jpg?v=1745622281</t>
         </is>
       </c>
       <c r="O794" s="2" t="n">
@@ -48036,7 +48036,7 @@
     </row>
     <row r="795">
       <c r="A795" s="2" t="n">
-        <v>8980488159453</v>
+        <v>8980487995613</v>
       </c>
       <c r="B795" s="2" t="inlineStr">
         <is>
@@ -48079,12 +48079,12 @@
       </c>
       <c r="M795" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-25</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-20</t>
         </is>
       </c>
       <c r="N795" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-10.58.49-AM.jpg?v=1745622281</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-10.59.40-AM.jpg?v=1745622281</t>
         </is>
       </c>
       <c r="O795" s="2" t="n">
@@ -48094,11 +48094,11 @@
     </row>
     <row r="796">
       <c r="A796" s="2" t="n">
-        <v>8980487995613</v>
+        <v>8980465189085</v>
       </c>
       <c r="B796" s="2" t="inlineStr">
         <is>
-          <t>Earcuff en Covergold Rodinado</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C796" s="2" t="inlineStr">
@@ -48137,12 +48137,12 @@
       </c>
       <c r="M796" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-20</t>
+          <t>https://www.gavajoyeria.com/products/a6-10</t>
         </is>
       </c>
       <c r="N796" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-28-at-10.59.40-AM.jpg?v=1745622281</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-06-27-at-4.28.05-PM.jpg?v=1745622206</t>
         </is>
       </c>
       <c r="O796" s="2" t="n">
@@ -48152,7 +48152,7 @@
     </row>
     <row r="797">
       <c r="A797" s="2" t="n">
-        <v>8980465189085</v>
+        <v>8980464828637</v>
       </c>
       <c r="B797" s="2" t="inlineStr">
         <is>
@@ -48195,12 +48195,12 @@
       </c>
       <c r="M797" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/a6-10</t>
+          <t>https://www.gavajoyeria.com/products/a6-6</t>
         </is>
       </c>
       <c r="N797" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-06-27-at-4.28.05-PM.jpg?v=1745622206</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-06-27-at-3.14.32-PM.jpg?v=1745622205</t>
         </is>
       </c>
       <c r="O797" s="2" t="n">
@@ -48210,11 +48210,11 @@
     </row>
     <row r="798">
       <c r="A798" s="2" t="n">
-        <v>8980464828637</v>
+        <v>8980489666781</v>
       </c>
       <c r="B798" s="2" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>Earcuff en Covergold Rodinado</t>
         </is>
       </c>
       <c r="C798" s="2" t="inlineStr">
@@ -48228,7 +48228,7 @@
         </is>
       </c>
       <c r="E798" s="3" t="n">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F798" s="3" t="n"/>
       <c r="G798" s="3" t="n"/>
@@ -48253,12 +48253,12 @@
       </c>
       <c r="M798" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/a6-6</t>
+          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-35</t>
         </is>
       </c>
       <c r="N798" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-06-27-at-3.14.32-PM.jpg?v=1745622205</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-05-at-3.21.48-PM_d9889e21-f3be-4a6c-930a-f7eaa13237dd.jpg?v=1745622285</t>
         </is>
       </c>
       <c r="O798" s="2" t="n">
@@ -48268,25 +48268,25 @@
     </row>
     <row r="799">
       <c r="A799" s="2" t="n">
-        <v>8980489666781</v>
+        <v>8980494254301</v>
       </c>
       <c r="B799" s="2" t="inlineStr">
         <is>
-          <t>Earcuff en Covergold Rodinado</t>
+          <t>Cadenas con Perla</t>
         </is>
       </c>
       <c r="C799" s="2" t="inlineStr">
         <is>
-          <t>Earcuff</t>
+          <t>Nueva Colección</t>
         </is>
       </c>
       <c r="D799" s="2" t="inlineStr">
         <is>
-          <t>Earcuff</t>
+          <t>Cadena</t>
         </is>
       </c>
       <c r="E799" s="3" t="n">
-        <v>5000</v>
+        <v>29000</v>
       </c>
       <c r="F799" s="3" t="n"/>
       <c r="G799" s="3" t="n"/>
@@ -48301,7 +48301,7 @@
       </c>
       <c r="K799" s="2" t="inlineStr">
         <is>
-          <t>earcuff</t>
+          <t>cadena</t>
         </is>
       </c>
       <c r="L799" s="2" t="inlineStr">
@@ -48311,40 +48311,40 @@
       </c>
       <c r="M799" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/earcuff-en-covergold-rodinado-35</t>
+          <t>https://www.gavajoyeria.com/products/cadenas-con-perla</t>
         </is>
       </c>
       <c r="N799" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-05-at-3.21.48-PM_d9889e21-f3be-4a6c-930a-f7eaa13237dd.jpg?v=1745622285</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-04-20-at-7.31.56-PM.jpg?v=1745622300</t>
         </is>
       </c>
       <c r="O799" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P799" s="2" t="inlineStr"/>
     </row>
     <row r="800">
       <c r="A800" s="2" t="n">
-        <v>8980494254301</v>
+        <v>8980493566173</v>
       </c>
       <c r="B800" s="2" t="inlineStr">
         <is>
-          <t>Cadenas con Perla</t>
+          <t>Pulsera con Corazon</t>
         </is>
       </c>
       <c r="C800" s="2" t="inlineStr">
         <is>
-          <t>Nueva Colección</t>
+          <t>Pulseras</t>
         </is>
       </c>
       <c r="D800" s="2" t="inlineStr">
         <is>
-          <t>Cadena</t>
+          <t>Pulseras</t>
         </is>
       </c>
       <c r="E800" s="3" t="n">
-        <v>29000</v>
+        <v>51000</v>
       </c>
       <c r="F800" s="3" t="n"/>
       <c r="G800" s="3" t="n"/>
@@ -48359,7 +48359,7 @@
       </c>
       <c r="K800" s="2" t="inlineStr">
         <is>
-          <t>cadena</t>
+          <t>pulseras</t>
         </is>
       </c>
       <c r="L800" s="2" t="inlineStr">
@@ -48369,26 +48369,26 @@
       </c>
       <c r="M800" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/cadenas-con-perla</t>
+          <t>https://www.gavajoyeria.com/products/pulsera-con-corazon</t>
         </is>
       </c>
       <c r="N800" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-04-20-at-7.31.56-PM.jpg?v=1745622300</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-04-20-at-9.15.26-PM.jpg?v=1745622298</t>
         </is>
       </c>
       <c r="O800" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P800" s="2" t="inlineStr"/>
     </row>
     <row r="801">
       <c r="A801" s="2" t="n">
-        <v>8980493566173</v>
+        <v>8980471742685</v>
       </c>
       <c r="B801" s="2" t="inlineStr">
         <is>
-          <t>Pulsera con Corazon</t>
+          <t>Pulsera de Mariquita</t>
         </is>
       </c>
       <c r="C801" s="2" t="inlineStr">
@@ -48402,7 +48402,7 @@
         </is>
       </c>
       <c r="E801" s="3" t="n">
-        <v>51000</v>
+        <v>49000</v>
       </c>
       <c r="F801" s="3" t="n"/>
       <c r="G801" s="3" t="n"/>
@@ -48427,26 +48427,26 @@
       </c>
       <c r="M801" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/pulsera-con-corazon</t>
+          <t>https://www.gavajoyeria.com/products/pulsera-de-mariquita</t>
         </is>
       </c>
       <c r="N801" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-04-20-at-9.15.26-PM.jpg?v=1745622298</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.12.38-PM.jpg?v=1745622227</t>
         </is>
       </c>
       <c r="O801" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P801" s="2" t="inlineStr"/>
     </row>
     <row r="802">
       <c r="A802" s="2" t="n">
-        <v>8980471742685</v>
+        <v>8980496318685</v>
       </c>
       <c r="B802" s="2" t="inlineStr">
         <is>
-          <t>Pulsera de Mariquita</t>
+          <t>Pulsera con Dije de Insectos</t>
         </is>
       </c>
       <c r="C802" s="2" t="inlineStr">
@@ -48460,7 +48460,7 @@
         </is>
       </c>
       <c r="E802" s="3" t="n">
-        <v>49000</v>
+        <v>38000</v>
       </c>
       <c r="F802" s="3" t="n"/>
       <c r="G802" s="3" t="n"/>
@@ -48485,26 +48485,26 @@
       </c>
       <c r="M802" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/pulsera-de-mariquita</t>
+          <t>https://www.gavajoyeria.com/products/pulsera-con-dije-de-insectos</t>
         </is>
       </c>
       <c r="N802" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-10-13-at-8.12.38-PM.jpg?v=1745622227</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-04-20-at-11.50.45-PM_54aa1f9a-e995-4bef-ba14-9db4349a4a63.jpg?v=1745622311</t>
         </is>
       </c>
       <c r="O802" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P802" s="2" t="inlineStr"/>
     </row>
     <row r="803">
       <c r="A803" s="2" t="n">
-        <v>8980496318685</v>
+        <v>8980491108573</v>
       </c>
       <c r="B803" s="2" t="inlineStr">
         <is>
-          <t>Pulsera con Dije de Insectos</t>
+          <t>Pulsera Covergold Rodinado</t>
         </is>
       </c>
       <c r="C803" s="2" t="inlineStr">
@@ -48518,7 +48518,7 @@
         </is>
       </c>
       <c r="E803" s="3" t="n">
-        <v>38000</v>
+        <v>29000</v>
       </c>
       <c r="F803" s="3" t="n"/>
       <c r="G803" s="3" t="n"/>
@@ -48543,26 +48543,30 @@
       </c>
       <c r="M803" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/pulsera-con-dije-de-insectos</t>
+          <t>https://www.gavajoyeria.com/products/set-en-covergold-rodinado-pulsera-8</t>
         </is>
       </c>
       <c r="N803" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-04-20-at-11.50.45-PM_54aa1f9a-e995-4bef-ba14-9db4349a4a63.jpg?v=1745622311</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-6.22.32-AM-3_9b79e17c-d0b7-4dde-ae14-2dc65cdaf496.jpg?v=1745622290</t>
         </is>
       </c>
       <c r="O803" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P803" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P803" s="2" t="inlineStr">
+        <is>
+          <t>Solo pulsera</t>
+        </is>
+      </c>
     </row>
     <row r="804">
       <c r="A804" s="2" t="n">
-        <v>8980491108573</v>
+        <v>8980482851037</v>
       </c>
       <c r="B804" s="2" t="inlineStr">
         <is>
-          <t>Pulsera Covergold Rodinado</t>
+          <t>Pulseras en Covergold Rodinado</t>
         </is>
       </c>
       <c r="C804" s="2" t="inlineStr">
@@ -48601,30 +48605,26 @@
       </c>
       <c r="M804" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/set-en-covergold-rodinado-pulsera-8</t>
+          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-13</t>
         </is>
       </c>
       <c r="N804" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-6.22.32-AM-3_9b79e17c-d0b7-4dde-ae14-2dc65cdaf496.jpg?v=1745622290</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-08-at-4.48.11-PM_c58bb01a-332a-49f4-a812-294f3e53089f.jpg?v=1745622264</t>
         </is>
       </c>
       <c r="O804" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P804" s="2" t="inlineStr">
-        <is>
-          <t>Solo pulsera</t>
-        </is>
-      </c>
+      <c r="P804" s="2" t="inlineStr"/>
     </row>
     <row r="805">
       <c r="A805" s="2" t="n">
-        <v>8980482851037</v>
+        <v>8980490125533</v>
       </c>
       <c r="B805" s="2" t="inlineStr">
         <is>
-          <t>Pulseras en Covergold Rodinado</t>
+          <t>Pulsera Covergold Rodinado</t>
         </is>
       </c>
       <c r="C805" s="2" t="inlineStr">
@@ -48638,7 +48638,7 @@
         </is>
       </c>
       <c r="E805" s="3" t="n">
-        <v>29000</v>
+        <v>28000</v>
       </c>
       <c r="F805" s="3" t="n"/>
       <c r="G805" s="3" t="n"/>
@@ -48663,22 +48663,26 @@
       </c>
       <c r="M805" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-13</t>
+          <t>https://www.gavajoyeria.com/products/set-en-covergold-rodinado-pulsera-6</t>
         </is>
       </c>
       <c r="N805" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-08-at-4.48.11-PM_c58bb01a-332a-49f4-a812-294f3e53089f.jpg?v=1745622264</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-6.22.32-AM-1_ff26cd83-84f4-421e-a988-66e4f0132d9c.jpg?v=1745622287</t>
         </is>
       </c>
       <c r="O805" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P805" s="2" t="inlineStr"/>
+      <c r="P805" s="2" t="inlineStr">
+        <is>
+          <t>solo Pulsera Covergold Rodinado</t>
+        </is>
+      </c>
     </row>
     <row r="806">
       <c r="A806" s="2" t="n">
-        <v>8980490125533</v>
+        <v>8980490551517</v>
       </c>
       <c r="B806" s="2" t="inlineStr">
         <is>
@@ -48696,7 +48700,7 @@
         </is>
       </c>
       <c r="E806" s="3" t="n">
-        <v>28000</v>
+        <v>25000</v>
       </c>
       <c r="F806" s="3" t="n"/>
       <c r="G806" s="3" t="n"/>
@@ -48721,12 +48725,12 @@
       </c>
       <c r="M806" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/set-en-covergold-rodinado-pulsera-6</t>
+          <t>https://www.gavajoyeria.com/products/set-en-covergold-rodinado-pulsera-11</t>
         </is>
       </c>
       <c r="N806" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-6.22.32-AM-1_ff26cd83-84f4-421e-a988-66e4f0132d9c.jpg?v=1745622287</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-6.25.28-AM_90f51885-f1a1-4019-a9ff-0b7c42b3b75e.jpg?v=1745622288</t>
         </is>
       </c>
       <c r="O806" s="2" t="n">
@@ -48734,17 +48738,17 @@
       </c>
       <c r="P806" s="2" t="inlineStr">
         <is>
-          <t>solo Pulsera Covergold Rodinado</t>
+          <t>Solo Pulsera Covergold Rodinado</t>
         </is>
       </c>
     </row>
     <row r="807">
       <c r="A807" s="2" t="n">
-        <v>8980490551517</v>
+        <v>8980482162909</v>
       </c>
       <c r="B807" s="2" t="inlineStr">
         <is>
-          <t>Pulsera Covergold Rodinado</t>
+          <t>Pulseras en Covergold Rodinado</t>
         </is>
       </c>
       <c r="C807" s="2" t="inlineStr">
@@ -48758,7 +48762,7 @@
         </is>
       </c>
       <c r="E807" s="3" t="n">
-        <v>25000</v>
+        <v>22000</v>
       </c>
       <c r="F807" s="3" t="n"/>
       <c r="G807" s="3" t="n"/>
@@ -48783,26 +48787,22 @@
       </c>
       <c r="M807" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/set-en-covergold-rodinado-pulsera-11</t>
+          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-9</t>
         </is>
       </c>
       <c r="N807" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-04-at-6.25.28-AM_90f51885-f1a1-4019-a9ff-0b7c42b3b75e.jpg?v=1745622288</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-08-at-5.01.15-PM.jpg?v=1745622262</t>
         </is>
       </c>
       <c r="O807" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P807" s="2" t="inlineStr">
-        <is>
-          <t>Solo Pulsera Covergold Rodinado</t>
-        </is>
-      </c>
+      <c r="P807" s="2" t="inlineStr"/>
     </row>
     <row r="808">
       <c r="A808" s="2" t="n">
-        <v>8980482162909</v>
+        <v>8980483375325</v>
       </c>
       <c r="B808" s="2" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         </is>
       </c>
       <c r="E808" s="3" t="n">
-        <v>22000</v>
+        <v>21000</v>
       </c>
       <c r="F808" s="3" t="n"/>
       <c r="G808" s="3" t="n"/>
@@ -48845,12 +48845,12 @@
       </c>
       <c r="M808" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-9</t>
+          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-28</t>
         </is>
       </c>
       <c r="N808" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-08-at-5.01.15-PM.jpg?v=1745622262</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-08-at-4.17.27-PM.jpg?v=1745622266</t>
         </is>
       </c>
       <c r="O808" s="2" t="n">
@@ -48860,11 +48860,11 @@
     </row>
     <row r="809">
       <c r="A809" s="2" t="n">
-        <v>8980483375325</v>
+        <v>8980473741533</v>
       </c>
       <c r="B809" s="2" t="inlineStr">
         <is>
-          <t>Pulseras en Covergold Rodinado</t>
+          <t>A21</t>
         </is>
       </c>
       <c r="C809" s="2" t="inlineStr">
@@ -48903,26 +48903,26 @@
       </c>
       <c r="M809" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-28</t>
+          <t>https://www.gavajoyeria.com/products/a21-2</t>
         </is>
       </c>
       <c r="N809" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-08-at-4.17.27-PM.jpg?v=1745622266</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-11-28-at-1.40.50-PM.jpg?v=1745622236</t>
         </is>
       </c>
       <c r="O809" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P809" s="2" t="inlineStr"/>
     </row>
     <row r="810">
       <c r="A810" s="2" t="n">
-        <v>8980473741533</v>
+        <v>8980494975197</v>
       </c>
       <c r="B810" s="2" t="inlineStr">
         <is>
-          <t>A21</t>
+          <t>Pulsera con Perla</t>
         </is>
       </c>
       <c r="C810" s="2" t="inlineStr">
@@ -48936,7 +48936,7 @@
         </is>
       </c>
       <c r="E810" s="3" t="n">
-        <v>21000</v>
+        <v>20000</v>
       </c>
       <c r="F810" s="3" t="n"/>
       <c r="G810" s="3" t="n"/>
@@ -48961,26 +48961,26 @@
       </c>
       <c r="M810" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/a21-2</t>
+          <t>https://www.gavajoyeria.com/products/pulsera-con-perla</t>
         </is>
       </c>
       <c r="N810" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-11-28-at-1.40.50-PM.jpg?v=1745622236</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-04-20-at-7.31.56-PM_87666961-a7af-4b1d-847e-baf52adf56f5.jpg?v=1745622302</t>
         </is>
       </c>
       <c r="O810" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P810" s="2" t="inlineStr"/>
     </row>
     <row r="811">
       <c r="A811" s="2" t="n">
-        <v>8980494975197</v>
+        <v>8980468596957</v>
       </c>
       <c r="B811" s="2" t="inlineStr">
         <is>
-          <t>Pulsera con Perla</t>
+          <t>Pulsera</t>
         </is>
       </c>
       <c r="C811" s="2" t="inlineStr">
@@ -49019,26 +49019,26 @@
       </c>
       <c r="M811" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/pulsera-con-perla</t>
+          <t>https://www.gavajoyeria.com/products/a9-30</t>
         </is>
       </c>
       <c r="N811" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-04-20-at-7.31.56-PM_87666961-a7af-4b1d-847e-baf52adf56f5.jpg?v=1745622302</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-08-22-at-5.10.29-PM.jpg?v=1745622216</t>
         </is>
       </c>
       <c r="O811" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P811" s="2" t="inlineStr"/>
     </row>
     <row r="812">
       <c r="A812" s="2" t="n">
-        <v>8980468596957</v>
+        <v>8980483703005</v>
       </c>
       <c r="B812" s="2" t="inlineStr">
         <is>
-          <t>Pulsera</t>
+          <t>Pulseras en Covergold Rodinado</t>
         </is>
       </c>
       <c r="C812" s="2" t="inlineStr">
@@ -49052,7 +49052,7 @@
         </is>
       </c>
       <c r="E812" s="3" t="n">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="F812" s="3" t="n"/>
       <c r="G812" s="3" t="n"/>
@@ -49077,12 +49077,12 @@
       </c>
       <c r="M812" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/a9-30</t>
+          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-38</t>
         </is>
       </c>
       <c r="N812" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-08-22-at-5.10.29-PM.jpg?v=1745622216</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/165c2758-6b8a-4879-8da3-8c57f6d5a6db.jpg?v=1745622267</t>
         </is>
       </c>
       <c r="O812" s="2" t="n">
@@ -49092,7 +49092,7 @@
     </row>
     <row r="813">
       <c r="A813" s="2" t="n">
-        <v>8980483703005</v>
+        <v>8980483309789</v>
       </c>
       <c r="B813" s="2" t="inlineStr">
         <is>
@@ -49135,12 +49135,12 @@
       </c>
       <c r="M813" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-38</t>
+          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-44</t>
         </is>
       </c>
       <c r="N813" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/165c2758-6b8a-4879-8da3-8c57f6d5a6db.jpg?v=1745622267</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/b2f5c389-9539-46a8-a4c2-1d04bfe268bc.jpg?v=1745622265</t>
         </is>
       </c>
       <c r="O813" s="2" t="n">
@@ -49150,7 +49150,7 @@
     </row>
     <row r="814">
       <c r="A814" s="2" t="n">
-        <v>8980483309789</v>
+        <v>8980480983261</v>
       </c>
       <c r="B814" s="2" t="inlineStr">
         <is>
@@ -49193,12 +49193,12 @@
       </c>
       <c r="M814" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-44</t>
+          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-16</t>
         </is>
       </c>
       <c r="N814" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/b2f5c389-9539-46a8-a4c2-1d04bfe268bc.jpg?v=1745622265</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-08-at-4.48.11-PM.jpg?v=1745622258</t>
         </is>
       </c>
       <c r="O814" s="2" t="n">
@@ -49208,7 +49208,7 @@
     </row>
     <row r="815">
       <c r="A815" s="2" t="n">
-        <v>8980480983261</v>
+        <v>8980481147101</v>
       </c>
       <c r="B815" s="2" t="inlineStr">
         <is>
@@ -49226,7 +49226,7 @@
         </is>
       </c>
       <c r="E815" s="3" t="n">
-        <v>19000</v>
+        <v>18000</v>
       </c>
       <c r="F815" s="3" t="n"/>
       <c r="G815" s="3" t="n"/>
@@ -49251,12 +49251,12 @@
       </c>
       <c r="M815" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-16</t>
+          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-21</t>
         </is>
       </c>
       <c r="N815" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-08-at-4.48.11-PM.jpg?v=1745622258</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-08-at-4.38.00-PM.jpg?v=1745622259</t>
         </is>
       </c>
       <c r="O815" s="2" t="n">
@@ -49266,7 +49266,7 @@
     </row>
     <row r="816">
       <c r="A816" s="2" t="n">
-        <v>8980481147101</v>
+        <v>8980483539165</v>
       </c>
       <c r="B816" s="2" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         </is>
       </c>
       <c r="E816" s="3" t="n">
-        <v>18000</v>
+        <v>17000</v>
       </c>
       <c r="F816" s="3" t="n"/>
       <c r="G816" s="3" t="n"/>
@@ -49309,12 +49309,12 @@
       </c>
       <c r="M816" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-21</t>
+          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-33</t>
         </is>
       </c>
       <c r="N816" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-08-at-4.38.00-PM.jpg?v=1745622259</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-08-at-12.13.01-PM.jpg?v=1745622266</t>
         </is>
       </c>
       <c r="O816" s="2" t="n">
@@ -49324,7 +49324,7 @@
     </row>
     <row r="817">
       <c r="A817" s="2" t="n">
-        <v>8980483539165</v>
+        <v>8980482425053</v>
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
@@ -49367,12 +49367,12 @@
       </c>
       <c r="M817" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-33</t>
+          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-19</t>
         </is>
       </c>
       <c r="N817" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-08-at-12.13.01-PM.jpg?v=1745622266</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-08-at-4.41.39-PM.jpg?v=1745622263</t>
         </is>
       </c>
       <c r="O817" s="2" t="n">
@@ -49382,7 +49382,7 @@
     </row>
     <row r="818">
       <c r="A818" s="2" t="n">
-        <v>8980482425053</v>
+        <v>8980481966301</v>
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
@@ -49425,12 +49425,12 @@
       </c>
       <c r="M818" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-19</t>
+          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-46</t>
         </is>
       </c>
       <c r="N818" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-08-at-4.41.39-PM.jpg?v=1745622263</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/48ba87e8-fd7b-43e8-bf76-4c9f854f7e54.jpg?v=1745622261</t>
         </is>
       </c>
       <c r="O818" s="2" t="n">
@@ -49440,7 +49440,7 @@
     </row>
     <row r="819">
       <c r="A819" s="2" t="n">
-        <v>8980481966301</v>
+        <v>8980481769693</v>
       </c>
       <c r="B819" s="2" t="inlineStr">
         <is>
@@ -49483,12 +49483,12 @@
       </c>
       <c r="M819" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-46</t>
+          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-41</t>
         </is>
       </c>
       <c r="N819" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/48ba87e8-fd7b-43e8-bf76-4c9f854f7e54.jpg?v=1745622261</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/4fad54b9-78c2-4730-beba-9c517e5eb63f.jpg?v=1745622261</t>
         </is>
       </c>
       <c r="O819" s="2" t="n">
@@ -49498,7 +49498,7 @@
     </row>
     <row r="820">
       <c r="A820" s="2" t="n">
-        <v>8980481769693</v>
+        <v>8980481343709</v>
       </c>
       <c r="B820" s="2" t="inlineStr">
         <is>
@@ -49541,12 +49541,12 @@
       </c>
       <c r="M820" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-41</t>
+          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-26</t>
         </is>
       </c>
       <c r="N820" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/4fad54b9-78c2-4730-beba-9c517e5eb63f.jpg?v=1745622261</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-08-at-4.21.35-PM.jpg?v=1745622259</t>
         </is>
       </c>
       <c r="O820" s="2" t="n">
@@ -49556,7 +49556,7 @@
     </row>
     <row r="821">
       <c r="A821" s="2" t="n">
-        <v>8980481343709</v>
+        <v>8980483834077</v>
       </c>
       <c r="B821" s="2" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         </is>
       </c>
       <c r="E821" s="3" t="n">
-        <v>17000</v>
+        <v>16000</v>
       </c>
       <c r="F821" s="3" t="n"/>
       <c r="G821" s="3" t="n"/>
@@ -49599,12 +49599,12 @@
       </c>
       <c r="M821" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-26</t>
+          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-43</t>
         </is>
       </c>
       <c r="N821" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-08-at-4.21.35-PM.jpg?v=1745622259</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/cc532367-0cc9-4384-96aa-3eb9654442cc.jpg?v=1745622268</t>
         </is>
       </c>
       <c r="O821" s="2" t="n">
@@ -49614,7 +49614,7 @@
     </row>
     <row r="822">
       <c r="A822" s="2" t="n">
-        <v>8980483834077</v>
+        <v>8980482228445</v>
       </c>
       <c r="B822" s="2" t="inlineStr">
         <is>
@@ -49657,12 +49657,12 @@
       </c>
       <c r="M822" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-43</t>
+          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-32</t>
         </is>
       </c>
       <c r="N822" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/cc532367-0cc9-4384-96aa-3eb9654442cc.jpg?v=1745622268</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-08-at-12.14.28-PM.jpg?v=1745622262</t>
         </is>
       </c>
       <c r="O822" s="2" t="n">
@@ -49672,7 +49672,7 @@
     </row>
     <row r="823">
       <c r="A823" s="2" t="n">
-        <v>8980482228445</v>
+        <v>8980481900765</v>
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
@@ -49715,12 +49715,12 @@
       </c>
       <c r="M823" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-32</t>
+          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-45</t>
         </is>
       </c>
       <c r="N823" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-08-at-12.14.28-PM.jpg?v=1745622262</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/fd573bf7-0472-421b-81e3-29b2448c401e.jpg?v=1745622262</t>
         </is>
       </c>
       <c r="O823" s="2" t="n">
@@ -49730,7 +49730,7 @@
     </row>
     <row r="824">
       <c r="A824" s="2" t="n">
-        <v>8980481900765</v>
+        <v>8980481245405</v>
       </c>
       <c r="B824" s="2" t="inlineStr">
         <is>
@@ -49773,12 +49773,12 @@
       </c>
       <c r="M824" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-45</t>
+          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-25</t>
         </is>
       </c>
       <c r="N824" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/fd573bf7-0472-421b-81e3-29b2448c401e.jpg?v=1745622262</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-08-at-4.25.59-PM.jpg?v=1745622259</t>
         </is>
       </c>
       <c r="O824" s="2" t="n">
@@ -49788,7 +49788,7 @@
     </row>
     <row r="825">
       <c r="A825" s="2" t="n">
-        <v>8980481245405</v>
+        <v>8980481409245</v>
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
@@ -49806,7 +49806,7 @@
         </is>
       </c>
       <c r="E825" s="3" t="n">
-        <v>16000</v>
+        <v>14000</v>
       </c>
       <c r="F825" s="3" t="n"/>
       <c r="G825" s="3" t="n"/>
@@ -49831,12 +49831,12 @@
       </c>
       <c r="M825" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-25</t>
+          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-30</t>
         </is>
       </c>
       <c r="N825" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-08-at-4.25.59-PM.jpg?v=1745622259</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-08-at-4.02.21-PM.jpg?v=1745622259</t>
         </is>
       </c>
       <c r="O825" s="2" t="n">
@@ -49846,25 +49846,25 @@
     </row>
     <row r="826">
       <c r="A826" s="2" t="n">
-        <v>8980481409245</v>
+        <v>8980485669085</v>
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>Pulseras en Covergold Rodinado</t>
+          <t>Topos en Coverd Gold</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
         <is>
-          <t>Pulseras</t>
+          <t>Topos</t>
         </is>
       </c>
       <c r="D826" s="2" t="inlineStr">
         <is>
-          <t>Pulseras</t>
+          <t>Topos</t>
         </is>
       </c>
       <c r="E826" s="3" t="n">
-        <v>14000</v>
+        <v>36000</v>
       </c>
       <c r="F826" s="3" t="n"/>
       <c r="G826" s="3" t="n"/>
@@ -49879,7 +49879,7 @@
       </c>
       <c r="K826" s="2" t="inlineStr">
         <is>
-          <t>pulseras</t>
+          <t>topos</t>
         </is>
       </c>
       <c r="L826" s="2" t="inlineStr">
@@ -49889,12 +49889,12 @@
       </c>
       <c r="M826" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/pulseras-en-covergold-rodinado-30</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-50</t>
         </is>
       </c>
       <c r="N826" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-08-at-4.02.21-PM.jpg?v=1745622259</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-4.02.00-PM.jpg?v=1745622273</t>
         </is>
       </c>
       <c r="O826" s="2" t="n">
@@ -49904,7 +49904,7 @@
     </row>
     <row r="827">
       <c r="A827" s="2" t="n">
-        <v>8980485669085</v>
+        <v>8980484718813</v>
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
@@ -49947,12 +49947,12 @@
       </c>
       <c r="M827" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-50</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-39</t>
         </is>
       </c>
       <c r="N827" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-4.02.00-PM.jpg?v=1745622273</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-6.30.03-PM.jpg?v=1745622270</t>
         </is>
       </c>
       <c r="O827" s="2" t="n">
@@ -49962,7 +49962,7 @@
     </row>
     <row r="828">
       <c r="A828" s="2" t="n">
-        <v>8980484718813</v>
+        <v>8980483571933</v>
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
@@ -50005,12 +50005,12 @@
       </c>
       <c r="M828" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-39</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-32</t>
         </is>
       </c>
       <c r="N828" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-6.30.03-PM.jpg?v=1745622270</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-6.09.24-PM.jpg?v=1745622267</t>
         </is>
       </c>
       <c r="O828" s="2" t="n">
@@ -50020,7 +50020,7 @@
     </row>
     <row r="829">
       <c r="A829" s="2" t="n">
-        <v>8980483571933</v>
+        <v>8980484128989</v>
       </c>
       <c r="B829" s="2" t="inlineStr">
         <is>
@@ -50063,12 +50063,12 @@
       </c>
       <c r="M829" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-32</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-38</t>
         </is>
       </c>
       <c r="N829" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-6.09.24-PM.jpg?v=1745622267</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-6.27.01-PM.jpg?v=1745622268</t>
         </is>
       </c>
       <c r="O829" s="2" t="n">
@@ -50078,7 +50078,7 @@
     </row>
     <row r="830">
       <c r="A830" s="2" t="n">
-        <v>8980484128989</v>
+        <v>8980483899613</v>
       </c>
       <c r="B830" s="2" t="inlineStr">
         <is>
@@ -50121,12 +50121,12 @@
       </c>
       <c r="M830" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-38</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-33</t>
         </is>
       </c>
       <c r="N830" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-6.27.01-PM.jpg?v=1745622268</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-6.11.27-PM.jpg?v=1745622268</t>
         </is>
       </c>
       <c r="O830" s="2" t="n">
@@ -50136,11 +50136,11 @@
     </row>
     <row r="831">
       <c r="A831" s="2" t="n">
-        <v>8980483899613</v>
+        <v>8980471054557</v>
       </c>
       <c r="B831" s="2" t="inlineStr">
         <is>
-          <t>Topos en Coverd Gold</t>
+          <t>Mini ojos turcos</t>
         </is>
       </c>
       <c r="C831" s="2" t="inlineStr">
@@ -50179,26 +50179,30 @@
       </c>
       <c r="M831" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-33</t>
+          <t>https://www.gavajoyeria.com/products/a18-46</t>
         </is>
       </c>
       <c r="N831" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-6.11.27-PM.jpg?v=1745622268</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-09-26-at-10.20.22-PM.jpg?v=1745622224</t>
         </is>
       </c>
       <c r="O831" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P831" s="2" t="inlineStr"/>
+      <c r="P831" s="2" t="inlineStr">
+        <is>
+          <t>Cuida tus accesorios y alarga su vida, estos tips te ayudarán a lograrlo: Evita el contacto con perfumes, sprays o cualquier otro químico fuerte. Guárdalos siempre por separado. Lávalos con jabón suave y agua, y asegúrate de secarlos muy bien. Evita usarlos al hacer ejercicio o en momentos donde la sudoración pueda ser mayor.</t>
+        </is>
+      </c>
     </row>
     <row r="832">
       <c r="A832" s="2" t="n">
-        <v>8980471054557</v>
+        <v>8980470694109</v>
       </c>
       <c r="B832" s="2" t="inlineStr">
         <is>
-          <t>Mini ojos turcos</t>
+          <t>Ojos turcos</t>
         </is>
       </c>
       <c r="C832" s="2" t="inlineStr">
@@ -50237,12 +50241,12 @@
       </c>
       <c r="M832" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/a18-46</t>
+          <t>https://www.gavajoyeria.com/products/a18-44</t>
         </is>
       </c>
       <c r="N832" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-09-26-at-10.20.22-PM.jpg?v=1745622224</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-09-26-at-10.12.40-PM.jpg?v=1745622223</t>
         </is>
       </c>
       <c r="O832" s="2" t="n">
@@ -50250,17 +50254,17 @@
       </c>
       <c r="P832" s="2" t="inlineStr">
         <is>
-          <t>Cuida tus accesorios y alarga su vida, estos tips te ayudarán a lograrlo: Evita el contacto con perfumes, sprays o cualquier otro químico fuerte. Guárdalos siempre por separado. Lávalos con jabón suave y agua, y asegúrate de secarlos muy bien. Evita usarlos al hacer ejercicio o en momentos donde la sudoración pueda ser mayor.</t>
+          <t>Cuida tus accesorios y alarga su vida, estos tips te ayudarán a lograrlo: Evita el contacto con perfumes, sprays o cualquier otro químico fuerte. Guárdalos siempre por separado. Lávalos con jabón suave y agua, y asegúrate de secarlos muy bien. Evita usarlos al hacer ejercicio o en momentos donde la sudoración pueda ser mayor. Set completo</t>
         </is>
       </c>
     </row>
     <row r="833">
       <c r="A833" s="2" t="n">
-        <v>8980470694109</v>
+        <v>8980469514461</v>
       </c>
       <c r="B833" s="2" t="inlineStr">
         <is>
-          <t>Ojos turcos</t>
+          <t>Mini topo virgen</t>
         </is>
       </c>
       <c r="C833" s="2" t="inlineStr">
@@ -50299,12 +50303,12 @@
       </c>
       <c r="M833" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/a18-44</t>
+          <t>https://www.gavajoyeria.com/products/a9-32</t>
         </is>
       </c>
       <c r="N833" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-09-26-at-10.12.40-PM.jpg?v=1745622223</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-08-16-at-5.41.04-PM.jpg?v=1745622219</t>
         </is>
       </c>
       <c r="O833" s="2" t="n">
@@ -50312,17 +50316,17 @@
       </c>
       <c r="P833" s="2" t="inlineStr">
         <is>
-          <t>Cuida tus accesorios y alarga su vida, estos tips te ayudarán a lograrlo: Evita el contacto con perfumes, sprays o cualquier otro químico fuerte. Guárdalos siempre por separado. Lávalos con jabón suave y agua, y asegúrate de secarlos muy bien. Evita usarlos al hacer ejercicio o en momentos donde la sudoración pueda ser mayor. Set completo</t>
+          <t>Cuida tus accesorios y alarga su vida, estos tips te ayudarán a lograrlo: Evita el contacto con perfumes, sprays o cualquier otro químico fuerte. Guárdalos siempre por separado. Lávalos con jabón suave y agua, y asegúrate de secarlos muy bien. Evita usarlos al hacer ejercicio o en momentos donde la sudoración pueda ser mayor.</t>
         </is>
       </c>
     </row>
     <row r="834">
       <c r="A834" s="2" t="n">
-        <v>8980469514461</v>
+        <v>8980462338269</v>
       </c>
       <c r="B834" s="2" t="inlineStr">
         <is>
-          <t>Mini topo virgen</t>
+          <t>Mini gota plateada</t>
         </is>
       </c>
       <c r="C834" s="2" t="inlineStr">
@@ -50361,12 +50365,12 @@
       </c>
       <c r="M834" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/a9-32</t>
+          <t>https://www.gavajoyeria.com/products/a18-7</t>
         </is>
       </c>
       <c r="N834" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-08-16-at-5.41.04-PM.jpg?v=1745622219</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-04-17-at-7.29.50-PM.jpg?v=1745622197</t>
         </is>
       </c>
       <c r="O834" s="2" t="n">
@@ -50380,11 +50384,11 @@
     </row>
     <row r="835">
       <c r="A835" s="2" t="n">
-        <v>8980462338269</v>
+        <v>8980461420765</v>
       </c>
       <c r="B835" s="2" t="inlineStr">
         <is>
-          <t>Mini gota plateada</t>
+          <t>Maxi gota</t>
         </is>
       </c>
       <c r="C835" s="2" t="inlineStr">
@@ -50398,7 +50402,7 @@
         </is>
       </c>
       <c r="E835" s="3" t="n">
-        <v>36000</v>
+        <v>30000</v>
       </c>
       <c r="F835" s="3" t="n"/>
       <c r="G835" s="3" t="n"/>
@@ -50423,12 +50427,12 @@
       </c>
       <c r="M835" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/a18-7</t>
+          <t>https://www.gavajoyeria.com/products/a20-12</t>
         </is>
       </c>
       <c r="N835" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-04-17-at-7.29.50-PM.jpg?v=1745622197</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-03-18-at-4.44.45-PM.jpg?v=1745622195</t>
         </is>
       </c>
       <c r="O835" s="2" t="n">
@@ -50442,11 +50446,11 @@
     </row>
     <row r="836">
       <c r="A836" s="2" t="n">
-        <v>8980461420765</v>
+        <v>8980486488285</v>
       </c>
       <c r="B836" s="2" t="inlineStr">
         <is>
-          <t>Maxi gota</t>
+          <t>Topos en Coverd Gold</t>
         </is>
       </c>
       <c r="C836" s="2" t="inlineStr">
@@ -50460,7 +50464,7 @@
         </is>
       </c>
       <c r="E836" s="3" t="n">
-        <v>30000</v>
+        <v>28000</v>
       </c>
       <c r="F836" s="3" t="n"/>
       <c r="G836" s="3" t="n"/>
@@ -50485,30 +50489,26 @@
       </c>
       <c r="M836" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/a20-12</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-54</t>
         </is>
       </c>
       <c r="N836" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-03-18-at-4.44.45-PM.jpg?v=1745622195</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-4.36.26-PM.jpg?v=1745622276</t>
         </is>
       </c>
       <c r="O836" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P836" s="2" t="inlineStr">
-        <is>
-          <t>Cuida tus accesorios y alarga su vida, estos tips te ayudarán a lograrlo: Evita el contacto con perfumes, sprays o cualquier otro químico fuerte. Guárdalos siempre por separado. Lávalos con jabón suave y agua, y asegúrate de secarlos muy bien. Evita usarlos al hacer ejercicio o en momentos donde la sudoración pueda ser mayor.</t>
-        </is>
-      </c>
+      <c r="P836" s="2" t="inlineStr"/>
     </row>
     <row r="837">
       <c r="A837" s="2" t="n">
-        <v>8980486488285</v>
+        <v>8980474036445</v>
       </c>
       <c r="B837" s="2" t="inlineStr">
         <is>
-          <t>Topos en Coverd Gold</t>
+          <t>Set de Topos</t>
         </is>
       </c>
       <c r="C837" s="2" t="inlineStr">
@@ -50547,22 +50547,26 @@
       </c>
       <c r="M837" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-54</t>
+          <t>https://www.gavajoyeria.com/products/set-de-topos-12</t>
         </is>
       </c>
       <c r="N837" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-4.36.26-PM.jpg?v=1745622276</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-11-28-at-2.33.38-PM.jpg?v=1745622236</t>
         </is>
       </c>
       <c r="O837" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P837" s="2" t="inlineStr"/>
+      <c r="P837" s="2" t="inlineStr">
+        <is>
+          <t>Cuida tus accesorios y alarga su vida, estos tips te ayudarán a lograrlo: Evita el contacto con perfumes, sprays o cualquier otro químico fuerte. Guárdalos siempre por separado. Lávalos con jabón suave y agua, y asegúrate de secarlos muy bien. Evita usarlos al hacer ejercicio o en momentos donde la sudoración pueda ser mayor.</t>
+        </is>
+      </c>
     </row>
     <row r="838">
       <c r="A838" s="2" t="n">
-        <v>8980474036445</v>
+        <v>8980474003677</v>
       </c>
       <c r="B838" s="2" t="inlineStr">
         <is>
@@ -50605,12 +50609,12 @@
       </c>
       <c r="M838" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/set-de-topos-12</t>
+          <t>https://www.gavajoyeria.com/products/set-de-topos-9</t>
         </is>
       </c>
       <c r="N838" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-11-28-at-2.33.38-PM.jpg?v=1745622236</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-11-28-at-2.27.21-PM.jpg?v=1745622236</t>
         </is>
       </c>
       <c r="O838" s="2" t="n">
@@ -50624,11 +50628,11 @@
     </row>
     <row r="839">
       <c r="A839" s="2" t="n">
-        <v>8980474003677</v>
+        <v>8980461551837</v>
       </c>
       <c r="B839" s="2" t="inlineStr">
         <is>
-          <t>Set de Topos</t>
+          <t>Topo esfera</t>
         </is>
       </c>
       <c r="C839" s="2" t="inlineStr">
@@ -50667,12 +50671,12 @@
       </c>
       <c r="M839" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/set-de-topos-9</t>
+          <t>https://www.gavajoyeria.com/products/a14-33</t>
         </is>
       </c>
       <c r="N839" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-11-28-at-2.27.21-PM.jpg?v=1745622236</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-03-18-at-4.53.00-PM.jpg?v=1745622195</t>
         </is>
       </c>
       <c r="O839" s="2" t="n">
@@ -50686,11 +50690,11 @@
     </row>
     <row r="840">
       <c r="A840" s="2" t="n">
-        <v>8980461551837</v>
+        <v>8980474560733</v>
       </c>
       <c r="B840" s="2" t="inlineStr">
         <is>
-          <t>Topo esfera</t>
+          <t>Set corazones</t>
         </is>
       </c>
       <c r="C840" s="2" t="inlineStr">
@@ -50704,7 +50708,7 @@
         </is>
       </c>
       <c r="E840" s="3" t="n">
-        <v>28000</v>
+        <v>26000</v>
       </c>
       <c r="F840" s="3" t="n"/>
       <c r="G840" s="3" t="n"/>
@@ -50729,12 +50733,12 @@
       </c>
       <c r="M840" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/a14-33</t>
+          <t>https://www.gavajoyeria.com/products/set-de-topos</t>
         </is>
       </c>
       <c r="N840" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-03-18-at-4.53.00-PM.jpg?v=1745622195</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-11-28-at-1.58.31-PM.jpg?v=1745622238</t>
         </is>
       </c>
       <c r="O840" s="2" t="n">
@@ -50748,11 +50752,11 @@
     </row>
     <row r="841">
       <c r="A841" s="2" t="n">
-        <v>8980474560733</v>
+        <v>8980464959709</v>
       </c>
       <c r="B841" s="2" t="inlineStr">
         <is>
-          <t>Set corazones</t>
+          <t>Maxi esferas</t>
         </is>
       </c>
       <c r="C841" s="2" t="inlineStr">
@@ -50791,12 +50795,12 @@
       </c>
       <c r="M841" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/set-de-topos</t>
+          <t>https://www.gavajoyeria.com/products/a13-32</t>
         </is>
       </c>
       <c r="N841" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-11-28-at-1.58.31-PM.jpg?v=1745622238</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-06-22-at-12.44.18-PM.jpg?v=1745622205</t>
         </is>
       </c>
       <c r="O841" s="2" t="n">
@@ -50810,11 +50814,11 @@
     </row>
     <row r="842">
       <c r="A842" s="2" t="n">
-        <v>8980464959709</v>
+        <v>8980483440861</v>
       </c>
       <c r="B842" s="2" t="inlineStr">
         <is>
-          <t>Maxi esferas</t>
+          <t>Topos en baguette doble función</t>
         </is>
       </c>
       <c r="C842" s="2" t="inlineStr">
@@ -50828,7 +50832,7 @@
         </is>
       </c>
       <c r="E842" s="3" t="n">
-        <v>26000</v>
+        <v>25000</v>
       </c>
       <c r="F842" s="3" t="n"/>
       <c r="G842" s="3" t="n"/>
@@ -50853,16 +50857,16 @@
       </c>
       <c r="M842" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/a13-32</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-27</t>
         </is>
       </c>
       <c r="N842" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-06-22-at-12.44.18-PM.jpg?v=1745622205</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-12.40.54-PM.jpg?v=1745622266</t>
         </is>
       </c>
       <c r="O842" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P842" s="2" t="inlineStr">
         <is>
@@ -50872,11 +50876,11 @@
     </row>
     <row r="843">
       <c r="A843" s="2" t="n">
-        <v>8980483440861</v>
+        <v>8980483080413</v>
       </c>
       <c r="B843" s="2" t="inlineStr">
         <is>
-          <t>Topos en baguette doble función</t>
+          <t>Topos doble función.</t>
         </is>
       </c>
       <c r="C843" s="2" t="inlineStr">
@@ -50915,12 +50919,12 @@
       </c>
       <c r="M843" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-27</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-17</t>
         </is>
       </c>
       <c r="N843" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-12.40.54-PM.jpg?v=1745622266</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-1.11.59-PM.jpg?v=1745622265</t>
         </is>
       </c>
       <c r="O843" s="2" t="n">
@@ -50934,11 +50938,11 @@
     </row>
     <row r="844">
       <c r="A844" s="2" t="n">
-        <v>8980483080413</v>
+        <v>8980482949341</v>
       </c>
       <c r="B844" s="2" t="inlineStr">
         <is>
-          <t>Topos doble función.</t>
+          <t>Topos perlas doble función</t>
         </is>
       </c>
       <c r="C844" s="2" t="inlineStr">
@@ -50977,12 +50981,12 @@
       </c>
       <c r="M844" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-17</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-12</t>
         </is>
       </c>
       <c r="N844" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-1.11.59-PM.jpg?v=1745622265</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-1.35.09-PM_d9741d0a-3821-4206-8f58-f3680b6170ce.jpg?v=1745622264</t>
         </is>
       </c>
       <c r="O844" s="2" t="n">
@@ -50996,11 +51000,11 @@
     </row>
     <row r="845">
       <c r="A845" s="2" t="n">
-        <v>8980482949341</v>
+        <v>8980483408093</v>
       </c>
       <c r="B845" s="2" t="inlineStr">
         <is>
-          <t>Topos perlas doble función</t>
+          <t>Topos doble función.</t>
         </is>
       </c>
       <c r="C845" s="2" t="inlineStr">
@@ -51039,12 +51043,12 @@
       </c>
       <c r="M845" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-12</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-23</t>
         </is>
       </c>
       <c r="N845" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-1.35.09-PM_d9741d0a-3821-4206-8f58-f3680b6170ce.jpg?v=1745622264</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-12.53.26-PM.jpg?v=1745622266</t>
         </is>
       </c>
       <c r="O845" s="2" t="n">
@@ -51058,7 +51062,7 @@
     </row>
     <row r="846">
       <c r="A846" s="2" t="n">
-        <v>8980483408093</v>
+        <v>8980483145949</v>
       </c>
       <c r="B846" s="2" t="inlineStr">
         <is>
@@ -51101,12 +51105,12 @@
       </c>
       <c r="M846" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-23</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-18</t>
         </is>
       </c>
       <c r="N846" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-12.53.26-PM.jpg?v=1745622266</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-1.09.32-PM.jpg?v=1745622265</t>
         </is>
       </c>
       <c r="O846" s="2" t="n">
@@ -51120,11 +51124,11 @@
     </row>
     <row r="847">
       <c r="A847" s="2" t="n">
-        <v>8980483145949</v>
+        <v>8980462239965</v>
       </c>
       <c r="B847" s="2" t="inlineStr">
         <is>
-          <t>Topos doble función.</t>
+          <t>Topo esfera dorado</t>
         </is>
       </c>
       <c r="C847" s="2" t="inlineStr">
@@ -51138,7 +51142,7 @@
         </is>
       </c>
       <c r="E847" s="3" t="n">
-        <v>25000</v>
+        <v>24000</v>
       </c>
       <c r="F847" s="3" t="n"/>
       <c r="G847" s="3" t="n"/>
@@ -51163,16 +51167,16 @@
       </c>
       <c r="M847" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-18</t>
+          <t>https://www.gavajoyeria.com/products/a12-7</t>
         </is>
       </c>
       <c r="N847" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-1.09.32-PM.jpg?v=1745622265</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-04-17-at-4.40.52-PM.jpg?v=1745622197</t>
         </is>
       </c>
       <c r="O847" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P847" s="2" t="inlineStr">
         <is>
@@ -51182,11 +51186,11 @@
     </row>
     <row r="848">
       <c r="A848" s="2" t="n">
-        <v>8980462239965</v>
+        <v>8980462010589</v>
       </c>
       <c r="B848" s="2" t="inlineStr">
         <is>
-          <t>Topo esfera dorado</t>
+          <t>Topos</t>
         </is>
       </c>
       <c r="C848" s="2" t="inlineStr">
@@ -51225,12 +51229,12 @@
       </c>
       <c r="M848" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/a12-7</t>
+          <t>https://www.gavajoyeria.com/products/a12-4</t>
         </is>
       </c>
       <c r="N848" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-04-17-at-4.40.52-PM.jpg?v=1745622197</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-04-17-at-4.40.51-PM.jpg?v=1745622197</t>
         </is>
       </c>
       <c r="O848" s="2" t="n">
@@ -51244,11 +51248,11 @@
     </row>
     <row r="849">
       <c r="A849" s="2" t="n">
-        <v>8980462010589</v>
+        <v>8980461945053</v>
       </c>
       <c r="B849" s="2" t="inlineStr">
         <is>
-          <t>Topos</t>
+          <t>Topo martillado</t>
         </is>
       </c>
       <c r="C849" s="2" t="inlineStr">
@@ -51287,12 +51291,12 @@
       </c>
       <c r="M849" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/a12-4</t>
+          <t>https://www.gavajoyeria.com/products/a12-22</t>
         </is>
       </c>
       <c r="N849" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-04-17-at-4.40.51-PM.jpg?v=1745622197</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-04-17-at-5.37.37-PM.jpg?v=1745622197</t>
         </is>
       </c>
       <c r="O849" s="2" t="n">
@@ -51306,11 +51310,11 @@
     </row>
     <row r="850">
       <c r="A850" s="2" t="n">
-        <v>8980461945053</v>
+        <v>8980462141661</v>
       </c>
       <c r="B850" s="2" t="inlineStr">
         <is>
-          <t>Topo martillado</t>
+          <t>Topo esfera</t>
         </is>
       </c>
       <c r="C850" s="2" t="inlineStr">
@@ -51349,12 +51353,12 @@
       </c>
       <c r="M850" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/a12-22</t>
+          <t>https://www.gavajoyeria.com/products/a12-30</t>
         </is>
       </c>
       <c r="N850" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-04-17-at-5.37.37-PM.jpg?v=1745622197</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-04-17-at-5.39.13-PM.jpg?v=1745622197</t>
         </is>
       </c>
       <c r="O850" s="2" t="n">
@@ -51368,11 +51372,11 @@
     </row>
     <row r="851">
       <c r="A851" s="2" t="n">
-        <v>8980462141661</v>
+        <v>8980487012573</v>
       </c>
       <c r="B851" s="2" t="inlineStr">
         <is>
-          <t>Topo esfera</t>
+          <t>Topos en Coverd Gold</t>
         </is>
       </c>
       <c r="C851" s="2" t="inlineStr">
@@ -51386,7 +51390,7 @@
         </is>
       </c>
       <c r="E851" s="3" t="n">
-        <v>24000</v>
+        <v>23000</v>
       </c>
       <c r="F851" s="3" t="n"/>
       <c r="G851" s="3" t="n"/>
@@ -51411,30 +51415,26 @@
       </c>
       <c r="M851" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/a12-30</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-69</t>
         </is>
       </c>
       <c r="N851" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-04-17-at-5.39.13-PM.jpg?v=1745622197</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-5.33.30-PM.jpg?v=1745622277</t>
         </is>
       </c>
       <c r="O851" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P851" s="2" t="inlineStr">
-        <is>
-          <t>Cuida tus accesorios y alarga su vida, estos tips te ayudarán a lograrlo: Evita el contacto con perfumes, sprays o cualquier otro químico fuerte. Guárdalos siempre por separado. Lávalos con jabón suave y agua, y asegúrate de secarlos muy bien. Evita usarlos al hacer ejercicio o en momentos donde la sudoración pueda ser mayor.</t>
-        </is>
-      </c>
+      <c r="P851" s="2" t="inlineStr"/>
     </row>
     <row r="852">
       <c r="A852" s="2" t="n">
-        <v>8980487012573</v>
+        <v>8980470923485</v>
       </c>
       <c r="B852" s="2" t="inlineStr">
         <is>
-          <t>Topos en Coverd Gold</t>
+          <t>Topo Guadalupe</t>
         </is>
       </c>
       <c r="C852" s="2" t="inlineStr">
@@ -51448,7 +51448,7 @@
         </is>
       </c>
       <c r="E852" s="3" t="n">
-        <v>23000</v>
+        <v>22000</v>
       </c>
       <c r="F852" s="3" t="n"/>
       <c r="G852" s="3" t="n"/>
@@ -51473,26 +51473,30 @@
       </c>
       <c r="M852" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-69</t>
+          <t>https://www.gavajoyeria.com/products/a11-6</t>
         </is>
       </c>
       <c r="N852" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-5.33.30-PM.jpg?v=1745622277</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-09-26-at-10.05.06-PM.jpg?v=1745622224</t>
         </is>
       </c>
       <c r="O852" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P852" s="2" t="inlineStr"/>
+      <c r="P852" s="2" t="inlineStr">
+        <is>
+          <t>Cuida tus accesorios y alarga su vida, estos tips te ayudarán a lograrlo: Evita el contacto con perfumes, sprays o cualquier otro químico fuerte. Guárdalos siempre por separado. Lávalos con jabón suave y agua, y asegúrate de secarlos muy bien. Evita usarlos al hacer ejercicio o en momentos donde la sudoración pueda ser mayor.</t>
+        </is>
+      </c>
     </row>
     <row r="853">
       <c r="A853" s="2" t="n">
-        <v>8980470923485</v>
+        <v>8980468433117</v>
       </c>
       <c r="B853" s="2" t="inlineStr">
         <is>
-          <t>Topo Guadalupe</t>
+          <t>Topo caracol</t>
         </is>
       </c>
       <c r="C853" s="2" t="inlineStr">
@@ -51531,12 +51535,12 @@
       </c>
       <c r="M853" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/a11-6</t>
+          <t>https://www.gavajoyeria.com/products/a11-37</t>
         </is>
       </c>
       <c r="N853" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-09-26-at-10.05.06-PM.jpg?v=1745622224</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-08-22-at-3.37.33-PM.jpg?v=1745622216</t>
         </is>
       </c>
       <c r="O853" s="2" t="n">
@@ -51550,11 +51554,11 @@
     </row>
     <row r="854">
       <c r="A854" s="2" t="n">
-        <v>8980468433117</v>
+        <v>8980492550365</v>
       </c>
       <c r="B854" s="2" t="inlineStr">
         <is>
-          <t>Topo caracol</t>
+          <t>Topos en Coverdgold rodinado con perla</t>
         </is>
       </c>
       <c r="C854" s="2" t="inlineStr">
@@ -51568,7 +51572,7 @@
         </is>
       </c>
       <c r="E854" s="3" t="n">
-        <v>22000</v>
+        <v>20000</v>
       </c>
       <c r="F854" s="3" t="n"/>
       <c r="G854" s="3" t="n"/>
@@ -51593,26 +51597,22 @@
       </c>
       <c r="M854" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/a11-37</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverdgold-rodinado-con-perla-22</t>
         </is>
       </c>
       <c r="N854" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-08-22-at-3.37.33-PM.jpg?v=1745622216</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-06-at-10.23.34-AM.jpg?v=1745622294</t>
         </is>
       </c>
       <c r="O854" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P854" s="2" t="inlineStr">
-        <is>
-          <t>Cuida tus accesorios y alarga su vida, estos tips te ayudarán a lograrlo: Evita el contacto con perfumes, sprays o cualquier otro químico fuerte. Guárdalos siempre por separado. Lávalos con jabón suave y agua, y asegúrate de secarlos muy bien. Evita usarlos al hacer ejercicio o en momentos donde la sudoración pueda ser mayor.</t>
-        </is>
-      </c>
+      <c r="P854" s="2" t="inlineStr"/>
     </row>
     <row r="855">
       <c r="A855" s="2" t="n">
-        <v>8980492550365</v>
+        <v>8980492091613</v>
       </c>
       <c r="B855" s="2" t="inlineStr">
         <is>
@@ -51655,12 +51655,12 @@
       </c>
       <c r="M855" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverdgold-rodinado-con-perla-22</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverdgold-rodinado-con-perla-20</t>
         </is>
       </c>
       <c r="N855" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-06-at-10.23.34-AM.jpg?v=1745622294</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-06-at-10.06.40-AM.jpg?v=1745622293</t>
         </is>
       </c>
       <c r="O855" s="2" t="n">
@@ -51670,7 +51670,7 @@
     </row>
     <row r="856">
       <c r="A856" s="2" t="n">
-        <v>8980492091613</v>
+        <v>8980490420445</v>
       </c>
       <c r="B856" s="2" t="inlineStr">
         <is>
@@ -51713,12 +51713,12 @@
       </c>
       <c r="M856" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverdgold-rodinado-con-perla-20</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverdgold-rodinado-con-perla-23</t>
         </is>
       </c>
       <c r="N856" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-06-at-10.06.40-AM.jpg?v=1745622293</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-06-at-10.26.33-AM.jpg?v=1745622288</t>
         </is>
       </c>
       <c r="O856" s="2" t="n">
@@ -51728,7 +51728,7 @@
     </row>
     <row r="857">
       <c r="A857" s="2" t="n">
-        <v>8980490420445</v>
+        <v>8980491665629</v>
       </c>
       <c r="B857" s="2" t="inlineStr">
         <is>
@@ -51771,12 +51771,12 @@
       </c>
       <c r="M857" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverdgold-rodinado-con-perla-23</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverdgold-rodinado-con-perla-24</t>
         </is>
       </c>
       <c r="N857" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-06-at-10.26.33-AM.jpg?v=1745622288</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-06-at-10.27.01-AM.jpg?v=1745622291</t>
         </is>
       </c>
       <c r="O857" s="2" t="n">
@@ -51786,7 +51786,7 @@
     </row>
     <row r="858">
       <c r="A858" s="2" t="n">
-        <v>8980491665629</v>
+        <v>8980491501789</v>
       </c>
       <c r="B858" s="2" t="inlineStr">
         <is>
@@ -51829,12 +51829,12 @@
       </c>
       <c r="M858" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverdgold-rodinado-con-perla-24</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverdgold-rodinado-con-perla-19</t>
         </is>
       </c>
       <c r="N858" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-06-at-10.27.01-AM.jpg?v=1745622291</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-06-at-9.57.12-AM.jpg?v=1745622291</t>
         </is>
       </c>
       <c r="O858" s="2" t="n">
@@ -51844,11 +51844,11 @@
     </row>
     <row r="859">
       <c r="A859" s="2" t="n">
-        <v>8980491501789</v>
+        <v>8980473675997</v>
       </c>
       <c r="B859" s="2" t="inlineStr">
         <is>
-          <t>Topos en Coverdgold rodinado con perla</t>
+          <t>Set de Topos</t>
         </is>
       </c>
       <c r="C859" s="2" t="inlineStr">
@@ -51887,26 +51887,30 @@
       </c>
       <c r="M859" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverdgold-rodinado-con-perla-19</t>
+          <t>https://www.gavajoyeria.com/products/set-de-topos-2</t>
         </is>
       </c>
       <c r="N859" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-06-at-9.57.12-AM.jpg?v=1745622291</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-11-28-at-2.02.51-PM.jpg?v=1745622235</t>
         </is>
       </c>
       <c r="O859" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P859" s="2" t="inlineStr"/>
+      <c r="P859" s="2" t="inlineStr">
+        <is>
+          <t>Cuida tus accesorios y alarga su vida, estos tips te ayudarán a lograrlo: Evita el contacto con perfumes, sprays o cualquier otro químico fuerte. Guárdalos siempre por separado. Lávalos con jabón suave y agua, y asegúrate de secarlos muy bien. Evita usarlos al hacer ejercicio o en momentos donde la sudoración pueda ser mayor.</t>
+        </is>
+      </c>
     </row>
     <row r="860">
       <c r="A860" s="2" t="n">
-        <v>8980473675997</v>
+        <v>8980492255453</v>
       </c>
       <c r="B860" s="2" t="inlineStr">
         <is>
-          <t>Set de Topos</t>
+          <t>Topos de presión en Coverdgold rodinado con perla</t>
         </is>
       </c>
       <c r="C860" s="2" t="inlineStr">
@@ -51920,7 +51924,7 @@
         </is>
       </c>
       <c r="E860" s="3" t="n">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="F860" s="3" t="n"/>
       <c r="G860" s="3" t="n"/>
@@ -51945,30 +51949,26 @@
       </c>
       <c r="M860" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/set-de-topos-2</t>
+          <t>https://www.gavajoyeria.com/products/topos-de-presion-en-coverdgold-rodinado-con-perla</t>
         </is>
       </c>
       <c r="N860" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-11-28-at-2.02.51-PM.jpg?v=1745622235</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-06-at-10.29.06-AM.jpg?v=1745622293</t>
         </is>
       </c>
       <c r="O860" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P860" s="2" t="inlineStr">
-        <is>
-          <t>Cuida tus accesorios y alarga su vida, estos tips te ayudarán a lograrlo: Evita el contacto con perfumes, sprays o cualquier otro químico fuerte. Guárdalos siempre por separado. Lávalos con jabón suave y agua, y asegúrate de secarlos muy bien. Evita usarlos al hacer ejercicio o en momentos donde la sudoración pueda ser mayor.</t>
-        </is>
-      </c>
+      <c r="P860" s="2" t="inlineStr"/>
     </row>
     <row r="861">
       <c r="A861" s="2" t="n">
-        <v>8980492255453</v>
+        <v>8980485636317</v>
       </c>
       <c r="B861" s="2" t="inlineStr">
         <is>
-          <t>Topos de presión en Coverdgold rodinado con perla</t>
+          <t>Topos en Coverd Gold</t>
         </is>
       </c>
       <c r="C861" s="2" t="inlineStr">
@@ -52007,12 +52007,12 @@
       </c>
       <c r="M861" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-de-presion-en-coverdgold-rodinado-con-perla</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-30</t>
         </is>
       </c>
       <c r="N861" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-03-06-at-10.29.06-AM.jpg?v=1745622293</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-6.03.10-PM.jpg?v=1745622273</t>
         </is>
       </c>
       <c r="O861" s="2" t="n">
@@ -52022,7 +52022,7 @@
     </row>
     <row r="862">
       <c r="A862" s="2" t="n">
-        <v>8980485636317</v>
+        <v>8980484882653</v>
       </c>
       <c r="B862" s="2" t="inlineStr">
         <is>
@@ -52065,22 +52065,22 @@
       </c>
       <c r="M862" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-30</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-10</t>
         </is>
       </c>
       <c r="N862" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-6.03.10-PM.jpg?v=1745622273</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-1.39.35-PM_9c55fa2d-562c-4671-ba06-4a213f7de35a.jpg?v=1745622271</t>
         </is>
       </c>
       <c r="O862" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P862" s="2" t="inlineStr"/>
     </row>
     <row r="863">
       <c r="A863" s="2" t="n">
-        <v>8980484882653</v>
+        <v>8980485767389</v>
       </c>
       <c r="B863" s="2" t="inlineStr">
         <is>
@@ -52123,22 +52123,22 @@
       </c>
       <c r="M863" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-10</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-55</t>
         </is>
       </c>
       <c r="N863" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-1.39.35-PM_9c55fa2d-562c-4671-ba06-4a213f7de35a.jpg?v=1745622271</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-4.38.23-PM.jpg?v=1745622274</t>
         </is>
       </c>
       <c r="O863" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P863" s="2" t="inlineStr"/>
     </row>
     <row r="864">
       <c r="A864" s="2" t="n">
-        <v>8980485767389</v>
+        <v>8980484325597</v>
       </c>
       <c r="B864" s="2" t="inlineStr">
         <is>
@@ -52181,12 +52181,12 @@
       </c>
       <c r="M864" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-55</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-56</t>
         </is>
       </c>
       <c r="N864" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-4.38.23-PM.jpg?v=1745622274</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-4.41.48-PM.jpg?v=1745622269</t>
         </is>
       </c>
       <c r="O864" s="2" t="n">
@@ -52196,7 +52196,7 @@
     </row>
     <row r="865">
       <c r="A865" s="2" t="n">
-        <v>8980484325597</v>
+        <v>8980484194525</v>
       </c>
       <c r="B865" s="2" t="inlineStr">
         <is>
@@ -52239,22 +52239,22 @@
       </c>
       <c r="M865" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-56</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-24</t>
         </is>
       </c>
       <c r="N865" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-4.41.48-PM.jpg?v=1745622269</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-12.49.51-PM.jpg?v=1745622268</t>
         </is>
       </c>
       <c r="O865" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P865" s="2" t="inlineStr"/>
     </row>
     <row r="866">
       <c r="A866" s="2" t="n">
-        <v>8980484194525</v>
+        <v>8980483997917</v>
       </c>
       <c r="B866" s="2" t="inlineStr">
         <is>
@@ -52297,12 +52297,12 @@
       </c>
       <c r="M866" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-24</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-19</t>
         </is>
       </c>
       <c r="N866" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-12.49.51-PM.jpg?v=1745622268</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-1.06.13-PM.jpg?v=1745622268</t>
         </is>
       </c>
       <c r="O866" s="2" t="n">
@@ -52312,7 +52312,7 @@
     </row>
     <row r="867">
       <c r="A867" s="2" t="n">
-        <v>8980483997917</v>
+        <v>8980483801309</v>
       </c>
       <c r="B867" s="2" t="inlineStr">
         <is>
@@ -52355,12 +52355,12 @@
       </c>
       <c r="M867" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-19</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-14</t>
         </is>
       </c>
       <c r="N867" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-1.06.13-PM.jpg?v=1745622268</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-1.28.27-PM.jpg?v=1745622267</t>
         </is>
       </c>
       <c r="O867" s="2" t="n">
@@ -52370,7 +52370,7 @@
     </row>
     <row r="868">
       <c r="A868" s="2" t="n">
-        <v>8980483801309</v>
+        <v>8980484489437</v>
       </c>
       <c r="B868" s="2" t="inlineStr">
         <is>
@@ -52413,12 +52413,12 @@
       </c>
       <c r="M868" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-14</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-16</t>
         </is>
       </c>
       <c r="N868" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-1.28.27-PM.jpg?v=1745622267</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-1.17.34-PM.jpg?v=1745622269</t>
         </is>
       </c>
       <c r="O868" s="2" t="n">
@@ -52428,7 +52428,7 @@
     </row>
     <row r="869">
       <c r="A869" s="2" t="n">
-        <v>8980484489437</v>
+        <v>8980484260061</v>
       </c>
       <c r="B869" s="2" t="inlineStr">
         <is>
@@ -52471,12 +52471,12 @@
       </c>
       <c r="M869" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-16</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-11</t>
         </is>
       </c>
       <c r="N869" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-1.17.34-PM.jpg?v=1745622269</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-1.37.32-PM.jpg?v=1745622269</t>
         </is>
       </c>
       <c r="O869" s="2" t="n">
@@ -52486,7 +52486,7 @@
     </row>
     <row r="870">
       <c r="A870" s="2" t="n">
-        <v>8980484260061</v>
+        <v>8980483277021</v>
       </c>
       <c r="B870" s="2" t="inlineStr">
         <is>
@@ -52529,12 +52529,12 @@
       </c>
       <c r="M870" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-11</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-22</t>
         </is>
       </c>
       <c r="N870" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-1.37.32-PM.jpg?v=1745622269</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-12.58.49-PM-1.jpg?v=1745622265</t>
         </is>
       </c>
       <c r="O870" s="2" t="n">
@@ -52544,7 +52544,7 @@
     </row>
     <row r="871">
       <c r="A871" s="2" t="n">
-        <v>8980483277021</v>
+        <v>8980485144797</v>
       </c>
       <c r="B871" s="2" t="inlineStr">
         <is>
@@ -52562,7 +52562,7 @@
         </is>
       </c>
       <c r="E871" s="3" t="n">
-        <v>19000</v>
+        <v>18000</v>
       </c>
       <c r="F871" s="3" t="n"/>
       <c r="G871" s="3" t="n"/>
@@ -52587,22 +52587,22 @@
       </c>
       <c r="M871" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-22</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-36</t>
         </is>
       </c>
       <c r="N871" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-12.58.49-PM-1.jpg?v=1745622265</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-6.23.18-PM.jpg?v=1745622272</t>
         </is>
       </c>
       <c r="O871" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P871" s="2" t="inlineStr"/>
     </row>
     <row r="872">
       <c r="A872" s="2" t="n">
-        <v>8980485144797</v>
+        <v>8980486848733</v>
       </c>
       <c r="B872" s="2" t="inlineStr">
         <is>
@@ -52620,7 +52620,7 @@
         </is>
       </c>
       <c r="E872" s="3" t="n">
-        <v>18000</v>
+        <v>16000</v>
       </c>
       <c r="F872" s="3" t="n"/>
       <c r="G872" s="3" t="n"/>
@@ -52645,12 +52645,12 @@
       </c>
       <c r="M872" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-36</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-64</t>
         </is>
       </c>
       <c r="N872" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-6.23.18-PM.jpg?v=1745622272</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-5.16.39-PM.jpg?v=1745622277</t>
         </is>
       </c>
       <c r="O872" s="2" t="n">
@@ -52660,7 +52660,7 @@
     </row>
     <row r="873">
       <c r="A873" s="2" t="n">
-        <v>8980486848733</v>
+        <v>8980485439709</v>
       </c>
       <c r="B873" s="2" t="inlineStr">
         <is>
@@ -52703,22 +52703,22 @@
       </c>
       <c r="M873" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-64</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-25</t>
         </is>
       </c>
       <c r="N873" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-5.16.39-PM.jpg?v=1745622277</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-12.46.09-PM-1_d498bd24-2b13-4479-99dd-6fafb722de53.jpg?v=1745622273</t>
         </is>
       </c>
       <c r="O873" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P873" s="2" t="inlineStr"/>
     </row>
     <row r="874">
       <c r="A874" s="2" t="n">
-        <v>8980485439709</v>
+        <v>8980485046493</v>
       </c>
       <c r="B874" s="2" t="inlineStr">
         <is>
@@ -52761,12 +52761,12 @@
       </c>
       <c r="M874" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-25</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-15</t>
         </is>
       </c>
       <c r="N874" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-12.46.09-PM-1_d498bd24-2b13-4479-99dd-6fafb722de53.jpg?v=1745622273</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-1.24.50-PM_f9ee76e6-0746-45cc-83dd-b0f061d5ed12.jpg?v=1745622271</t>
         </is>
       </c>
       <c r="O874" s="2" t="n">
@@ -52776,7 +52776,7 @@
     </row>
     <row r="875">
       <c r="A875" s="2" t="n">
-        <v>8980485046493</v>
+        <v>8980485931229</v>
       </c>
       <c r="B875" s="2" t="inlineStr">
         <is>
@@ -52819,22 +52819,22 @@
       </c>
       <c r="M875" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-15</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-60</t>
         </is>
       </c>
       <c r="N875" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-1.24.50-PM_f9ee76e6-0746-45cc-83dd-b0f061d5ed12.jpg?v=1745622271</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-4.55.59-PM.jpg?v=1745622274</t>
         </is>
       </c>
       <c r="O875" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P875" s="2" t="inlineStr"/>
     </row>
     <row r="876">
       <c r="A876" s="2" t="n">
-        <v>8980485931229</v>
+        <v>8980485603549</v>
       </c>
       <c r="B876" s="2" t="inlineStr">
         <is>
@@ -52877,12 +52877,12 @@
       </c>
       <c r="M876" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-60</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-63</t>
         </is>
       </c>
       <c r="N876" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-4.55.59-PM.jpg?v=1745622274</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-5.14.22-PM.jpg?v=1745622273</t>
         </is>
       </c>
       <c r="O876" s="2" t="n">
@@ -52892,7 +52892,7 @@
     </row>
     <row r="877">
       <c r="A877" s="2" t="n">
-        <v>8980485603549</v>
+        <v>8980484784349</v>
       </c>
       <c r="B877" s="2" t="inlineStr">
         <is>
@@ -52935,12 +52935,12 @@
       </c>
       <c r="M877" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-63</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-71</t>
         </is>
       </c>
       <c r="N877" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-5.14.22-PM.jpg?v=1745622273</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-5.40.13-PM.jpg?v=1745622270</t>
         </is>
       </c>
       <c r="O877" s="2" t="n">
@@ -52950,7 +52950,7 @@
     </row>
     <row r="878">
       <c r="A878" s="2" t="n">
-        <v>8980484784349</v>
+        <v>8980485243101</v>
       </c>
       <c r="B878" s="2" t="inlineStr">
         <is>
@@ -52993,12 +52993,12 @@
       </c>
       <c r="M878" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-71</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-53</t>
         </is>
       </c>
       <c r="N878" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-5.40.13-PM.jpg?v=1745622270</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-4.30.42-PM.jpg?v=1745622272</t>
         </is>
       </c>
       <c r="O878" s="2" t="n">
@@ -53008,7 +53008,7 @@
     </row>
     <row r="879">
       <c r="A879" s="2" t="n">
-        <v>8980485243101</v>
+        <v>8980484980957</v>
       </c>
       <c r="B879" s="2" t="inlineStr">
         <is>
@@ -53051,12 +53051,12 @@
       </c>
       <c r="M879" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-53</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-31</t>
         </is>
       </c>
       <c r="N879" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-4.30.42-PM.jpg?v=1745622272</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-6.05.53-PM.jpg?v=1745622271</t>
         </is>
       </c>
       <c r="O879" s="2" t="n">
@@ -53066,7 +53066,7 @@
     </row>
     <row r="880">
       <c r="A880" s="2" t="n">
-        <v>8980484980957</v>
+        <v>8980484653277</v>
       </c>
       <c r="B880" s="2" t="inlineStr">
         <is>
@@ -53109,22 +53109,22 @@
       </c>
       <c r="M880" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-31</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-21</t>
         </is>
       </c>
       <c r="N880" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-6.05.53-PM.jpg?v=1745622271</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-1.02.03-PM.jpg?v=1745622270</t>
         </is>
       </c>
       <c r="O880" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P880" s="2" t="inlineStr"/>
     </row>
     <row r="881">
       <c r="A881" s="2" t="n">
-        <v>8980484653277</v>
+        <v>8980486717661</v>
       </c>
       <c r="B881" s="2" t="inlineStr">
         <is>
@@ -53142,7 +53142,7 @@
         </is>
       </c>
       <c r="E881" s="3" t="n">
-        <v>16000</v>
+        <v>15000</v>
       </c>
       <c r="F881" s="3" t="n"/>
       <c r="G881" s="3" t="n"/>
@@ -53167,26 +53167,26 @@
       </c>
       <c r="M881" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-21</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-59</t>
         </is>
       </c>
       <c r="N881" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-1.02.03-PM.jpg?v=1745622270</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-4.49.40-PM.jpg?v=1745622276</t>
         </is>
       </c>
       <c r="O881" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P881" s="2" t="inlineStr"/>
     </row>
     <row r="882">
       <c r="A882" s="2" t="n">
-        <v>8980486717661</v>
+        <v>8980489404637</v>
       </c>
       <c r="B882" s="2" t="inlineStr">
         <is>
-          <t>Topos en Coverd Gold</t>
+          <t>Topos en Coverdgold Rodinado</t>
         </is>
       </c>
       <c r="C882" s="2" t="inlineStr">
@@ -53200,7 +53200,7 @@
         </is>
       </c>
       <c r="E882" s="3" t="n">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="F882" s="3" t="n"/>
       <c r="G882" s="3" t="n"/>
@@ -53225,12 +53225,12 @@
       </c>
       <c r="M882" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-59</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverdgold-rodinado-9</t>
         </is>
       </c>
       <c r="N882" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-4.49.40-PM.jpg?v=1745622276</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-04-at-6.11.09-PM.jpg?v=1745622285</t>
         </is>
       </c>
       <c r="O882" s="2" t="n">
@@ -53240,11 +53240,11 @@
     </row>
     <row r="883">
       <c r="A883" s="2" t="n">
-        <v>8980489404637</v>
+        <v>8980484096221</v>
       </c>
       <c r="B883" s="2" t="inlineStr">
         <is>
-          <t>Topos en Coverdgold Rodinado</t>
+          <t>Set de Topos</t>
         </is>
       </c>
       <c r="C883" s="2" t="inlineStr">
@@ -53283,12 +53283,12 @@
       </c>
       <c r="M883" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverdgold-rodinado-9</t>
+          <t>https://www.gavajoyeria.com/products/set-de-topos-19</t>
         </is>
       </c>
       <c r="N883" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-04-at-6.11.09-PM.jpg?v=1745622285</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-2.44.59-PM.jpg?v=1745622268</t>
         </is>
       </c>
       <c r="O883" s="2" t="n">
@@ -53298,11 +53298,11 @@
     </row>
     <row r="884">
       <c r="A884" s="2" t="n">
-        <v>8980484096221</v>
+        <v>8980491796701</v>
       </c>
       <c r="B884" s="2" t="inlineStr">
         <is>
-          <t>Set de Topos</t>
+          <t>Topos en Coverdgold rodinado con perla</t>
         </is>
       </c>
       <c r="C884" s="2" t="inlineStr">
@@ -53316,7 +53316,7 @@
         </is>
       </c>
       <c r="E884" s="3" t="n">
-        <v>13000</v>
+        <v>12000</v>
       </c>
       <c r="F884" s="3" t="n"/>
       <c r="G884" s="3" t="n"/>
@@ -53341,12 +53341,12 @@
       </c>
       <c r="M884" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/set-de-topos-19</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverdgold-rodinado-con-perla-9</t>
         </is>
       </c>
       <c r="N884" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-2.44.59-PM.jpg?v=1745622268</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-05-at-12.46.28-PM.jpg?v=1745622292</t>
         </is>
       </c>
       <c r="O884" s="2" t="n">
@@ -53356,7 +53356,7 @@
     </row>
     <row r="885">
       <c r="A885" s="2" t="n">
-        <v>8980491796701</v>
+        <v>8980491141341</v>
       </c>
       <c r="B885" s="2" t="inlineStr">
         <is>
@@ -53399,12 +53399,12 @@
       </c>
       <c r="M885" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverdgold-rodinado-con-perla-9</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverdgold-rodinado-con-perla-15</t>
         </is>
       </c>
       <c r="N885" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-05-at-12.46.28-PM.jpg?v=1745622292</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-05-at-12.03.35-PM.jpg?v=1745622290</t>
         </is>
       </c>
       <c r="O885" s="2" t="n">
@@ -53414,11 +53414,11 @@
     </row>
     <row r="886">
       <c r="A886" s="2" t="n">
-        <v>8980491141341</v>
+        <v>8980485538013</v>
       </c>
       <c r="B886" s="2" t="inlineStr">
         <is>
-          <t>Topos en Coverdgold rodinado con perla</t>
+          <t>Topos en Coverd Gold</t>
         </is>
       </c>
       <c r="C886" s="2" t="inlineStr">
@@ -53457,12 +53457,12 @@
       </c>
       <c r="M886" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverdgold-rodinado-con-perla-15</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-67</t>
         </is>
       </c>
       <c r="N886" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-05-at-12.03.35-PM.jpg?v=1745622290</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-5.29.27-PM.jpg?v=1745622274</t>
         </is>
       </c>
       <c r="O886" s="2" t="n">
@@ -53472,7 +53472,7 @@
     </row>
     <row r="887">
       <c r="A887" s="2" t="n">
-        <v>8980485538013</v>
+        <v>8980484849885</v>
       </c>
       <c r="B887" s="2" t="inlineStr">
         <is>
@@ -53515,26 +53515,26 @@
       </c>
       <c r="M887" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-67</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-26</t>
         </is>
       </c>
       <c r="N887" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-06-at-5.29.27-PM.jpg?v=1745622274</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-12.41.08-PM_a8bd9470-c723-4343-b2ab-47dcf8c29ee8.jpg?v=1745622271</t>
         </is>
       </c>
       <c r="O887" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P887" s="2" t="inlineStr"/>
     </row>
     <row r="888">
       <c r="A888" s="2" t="n">
-        <v>8980484849885</v>
+        <v>8980490879197</v>
       </c>
       <c r="B888" s="2" t="inlineStr">
         <is>
-          <t>Topos en Coverd Gold</t>
+          <t>Topos en Coverdgold rodinado con perla</t>
         </is>
       </c>
       <c r="C888" s="2" t="inlineStr">
@@ -53548,7 +53548,7 @@
         </is>
       </c>
       <c r="E888" s="3" t="n">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="F888" s="3" t="n"/>
       <c r="G888" s="3" t="n"/>
@@ -53573,26 +53573,26 @@
       </c>
       <c r="M888" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-26</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverdgold-rodinado-con-perla-18</t>
         </is>
       </c>
       <c r="N888" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-12.41.08-PM_a8bd9470-c723-4343-b2ab-47dcf8c29ee8.jpg?v=1745622271</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-05-at-11.36.11-AM.jpg?v=1745622289</t>
         </is>
       </c>
       <c r="O888" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P888" s="2" t="inlineStr"/>
     </row>
     <row r="889">
       <c r="A889" s="2" t="n">
-        <v>8980490879197</v>
+        <v>8980486127837</v>
       </c>
       <c r="B889" s="2" t="inlineStr">
         <is>
-          <t>Topos en Coverdgold rodinado con perla</t>
+          <t>Topos en Coverd Gold</t>
         </is>
       </c>
       <c r="C889" s="2" t="inlineStr">
@@ -53631,12 +53631,12 @@
       </c>
       <c r="M889" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverdgold-rodinado-con-perla-18</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-45</t>
         </is>
       </c>
       <c r="N889" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-05-at-11.36.11-AM.jpg?v=1745622289</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-10.25.46-AM.jpg?v=1745622275</t>
         </is>
       </c>
       <c r="O889" s="2" t="n">
@@ -53646,7 +53646,7 @@
     </row>
     <row r="890">
       <c r="A890" s="2" t="n">
-        <v>8980486127837</v>
+        <v>8980485963997</v>
       </c>
       <c r="B890" s="2" t="inlineStr">
         <is>
@@ -53689,12 +53689,12 @@
       </c>
       <c r="M890" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-45</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-40</t>
         </is>
       </c>
       <c r="N890" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-10.25.46-AM.jpg?v=1745622275</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-10.09.01-AM.jpg?v=1745622275</t>
         </is>
       </c>
       <c r="O890" s="2" t="n">
@@ -53704,7 +53704,7 @@
     </row>
     <row r="891">
       <c r="A891" s="2" t="n">
-        <v>8980485963997</v>
+        <v>8980485472477</v>
       </c>
       <c r="B891" s="2" t="inlineStr">
         <is>
@@ -53747,12 +53747,12 @@
       </c>
       <c r="M891" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-40</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-46</t>
         </is>
       </c>
       <c r="N891" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-10.09.01-AM.jpg?v=1745622275</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-10.28.52-AM.jpg?v=1745622273</t>
         </is>
       </c>
       <c r="O891" s="2" t="n">
@@ -53762,7 +53762,7 @@
     </row>
     <row r="892">
       <c r="A892" s="2" t="n">
-        <v>8980485472477</v>
+        <v>8980485308637</v>
       </c>
       <c r="B892" s="2" t="inlineStr">
         <is>
@@ -53805,12 +53805,12 @@
       </c>
       <c r="M892" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-46</t>
+          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-41</t>
         </is>
       </c>
       <c r="N892" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-10.28.52-AM.jpg?v=1745622273</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-10.11.58-AM.jpg?v=1745622272</t>
         </is>
       </c>
       <c r="O892" s="2" t="n">
@@ -53820,11 +53820,11 @@
     </row>
     <row r="893">
       <c r="A893" s="2" t="n">
-        <v>8980485308637</v>
+        <v>8980474888413</v>
       </c>
       <c r="B893" s="2" t="inlineStr">
         <is>
-          <t>Topos en Coverd Gold</t>
+          <t>Set de Topos</t>
         </is>
       </c>
       <c r="C893" s="2" t="inlineStr">
@@ -53838,7 +53838,7 @@
         </is>
       </c>
       <c r="E893" s="3" t="n">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="F893" s="3" t="n"/>
       <c r="G893" s="3" t="n"/>
@@ -53863,12 +53863,12 @@
       </c>
       <c r="M893" s="2" t="inlineStr">
         <is>
-          <t>https://www.gavajoyeria.com/products/topos-en-coverd-gold-41</t>
+          <t>https://www.gavajoyeria.com/products/set-de-topos-11</t>
         </is>
       </c>
       <c r="N893" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2025-02-07-at-10.11.58-AM.jpg?v=1745622272</t>
+          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-11-28-at-2.32.16-PM.jpg?v=1745622239</t>
         </is>
       </c>
       <c r="O893" s="2" t="n">
@@ -53876,66 +53876,8 @@
       </c>
       <c r="P893" s="2" t="inlineStr"/>
     </row>
-    <row r="894">
-      <c r="A894" s="2" t="n">
-        <v>8980474888413</v>
-      </c>
-      <c r="B894" s="2" t="inlineStr">
-        <is>
-          <t>Set de Topos</t>
-        </is>
-      </c>
-      <c r="C894" s="2" t="inlineStr">
-        <is>
-          <t>Topos</t>
-        </is>
-      </c>
-      <c r="D894" s="2" t="inlineStr">
-        <is>
-          <t>Topos</t>
-        </is>
-      </c>
-      <c r="E894" s="3" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F894" s="3" t="n"/>
-      <c r="G894" s="3" t="n"/>
-      <c r="H894" s="2" t="n"/>
-      <c r="I894" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J894" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="K894" s="2" t="inlineStr">
-        <is>
-          <t>topos</t>
-        </is>
-      </c>
-      <c r="L894" s="2" t="inlineStr">
-        <is>
-          <t>Gava Joyería</t>
-        </is>
-      </c>
-      <c r="M894" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gavajoyeria.com/products/set-de-topos-11</t>
-        </is>
-      </c>
-      <c r="N894" s="2" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0755/0605/7437/files/WhatsApp-Image-2024-11-28-at-2.32.16-PM.jpg?v=1745622239</t>
-        </is>
-      </c>
-      <c r="O894" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P894" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P894"/>
+  <autoFilter ref="A1:P893"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -53981,7 +53923,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
@@ -53993,7 +53935,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="5">
@@ -54024,7 +53966,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-13 14:49</t>
+          <t>2026-10-13 15:46</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$893</definedName>
@@ -53966,7 +53966,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-13 15:46</t>
+          <t>2026-10-14 00:35</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -53966,7 +53966,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:35</t>
+          <t>2026-10-14 06:33</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -53966,7 +53966,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 06:33</t>
+          <t>2026-10-14 12:35</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -53096,7 +53096,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 18:34</t>
+          <t>2026-10-15 00:34</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -53096,7 +53096,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-15 00:34</t>
+          <t>2026-10-15 06:34</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -53096,7 +53096,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-15 06:34</t>
+          <t>2026-10-15 12:35</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -53096,7 +53096,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-15 12:35</t>
+          <t>2026-10-15 18:30</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -54736,7 +54736,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-16 06:33</t>
+          <t>2026-10-16 12:34</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55670,7 +55670,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-17 00:33</t>
+          <t>2026-10-17 06:29</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55670,7 +55670,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-17 06:29</t>
+          <t>2026-10-17 12:27</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55670,7 +55670,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-17 12:27</t>
+          <t>2026-10-17 18:24</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55670,7 +55670,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-17 18:24</t>
+          <t>2026-10-18 00:33</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55670,7 +55670,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-18 00:33</t>
+          <t>2026-10-18 06:29</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55670,7 +55670,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-18 06:29</t>
+          <t>2026-10-18 12:27</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55670,7 +55670,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-18 12:27</t>
+          <t>2026-10-18 18:24</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55670,7 +55670,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-18 18:24</t>
+          <t>2026-10-19 00:34</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55670,7 +55670,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-19 00:34</t>
+          <t>2026-10-19 06:39</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55670,7 +55670,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-19 06:39</t>
+          <t>2026-10-19 12:37</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55670,7 +55670,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-19 12:37</t>
+          <t>2026-10-19 18:30</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55670,7 +55670,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-19 18:30</t>
+          <t>2026-10-20 00:36</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55670,7 +55670,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 00:36</t>
+          <t>2026-10-20 07:00</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55670,7 +55670,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 07:00</t>
+          <t>2026-10-20 12:34</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55670,7 +55670,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 12:34</t>
+          <t>2026-10-20 18:31</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55670,7 +55670,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 18:31</t>
+          <t>2026-10-21 00:34</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55670,7 +55670,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-21 00:34</t>
+          <t>2026-10-21 06:35</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$919</definedName>
@@ -55670,7 +55670,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-21 06:35</t>
+          <t>2026-10-21 01:56</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55670,7 +55670,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-21 01:56</t>
+          <t>2026-10-21 02:48</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55670,7 +55670,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-21 02:48</t>
+          <t>2026-10-21 03:31</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55670,7 +55670,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-21 03:31</t>
+          <t>2026-10-21 04:22</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$919</definedName>
@@ -55670,7 +55670,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-21 04:22</t>
+          <t>2026-10-21 12:35</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$919</definedName>
@@ -55670,7 +55670,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-21 12:35</t>
+          <t>2026-10-21 08:02</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$919</definedName>
@@ -55670,7 +55670,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-21 08:02</t>
+          <t>2026-10-21 18:30</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55550,7 +55550,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-22 00:35</t>
+          <t>2026-10-22 06:35</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55550,7 +55550,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-22 06:35</t>
+          <t>2026-10-22 12:36</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55550,7 +55550,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-22 12:36</t>
+          <t>2026-10-22 18:30</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55492,7 +55492,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-23 00:37</t>
+          <t>2026-10-23 06:34</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55492,7 +55492,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-23 06:34</t>
+          <t>2026-10-23 12:31</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55318,7 +55318,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-23 18:30</t>
+          <t>2026-10-24 00:40</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55318,7 +55318,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-24 00:40</t>
+          <t>2026-10-24 06:29</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55318,7 +55318,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-24 06:29</t>
+          <t>2026-10-24 12:28</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55318,7 +55318,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-24 12:28</t>
+          <t>2026-10-24 18:25</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55318,7 +55318,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-24 18:25</t>
+          <t>2026-10-25 00:30</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55318,7 +55318,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-25 00:30</t>
+          <t>2026-10-25 06:31</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55318,7 +55318,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-25 06:31</t>
+          <t>2026-10-25 12:28</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55318,7 +55318,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-25 12:28</t>
+          <t>2026-10-25 18:25</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55318,7 +55318,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-25 18:25</t>
+          <t>2026-10-26 00:43</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55318,7 +55318,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 00:43</t>
+          <t>2026-10-26 06:40</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55318,7 +55318,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 06:40</t>
+          <t>2026-10-26 14:42</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55318,7 +55318,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 14:42</t>
+          <t>2026-10-26 18:40</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55318,7 +55318,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 18:40</t>
+          <t>2026-10-27 00:34</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55318,7 +55318,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 00:34</t>
+          <t>2026-10-27 06:37</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55318,7 +55318,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 06:37</t>
+          <t>2026-10-27 12:39</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55318,7 +55318,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 12:39</t>
+          <t>2026-10-27 18:40</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55318,7 +55318,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 18:40</t>
+          <t>2026-10-28 00:44</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55318,7 +55318,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-28 00:44</t>
+          <t>2026-10-28 06:43</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55318,7 +55318,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-28 06:43</t>
+          <t>2026-10-28 12:44</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55318,7 +55318,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-28 12:44</t>
+          <t>2026-10-28 18:41</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55318,7 +55318,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-28 18:41</t>
+          <t>2026-10-29 00:44</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55318,7 +55318,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-29 00:44</t>
+          <t>2026-10-29 06:46</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55318,7 +55318,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-29 06:46</t>
+          <t>2026-10-29 12:46</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55198,7 +55198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 00:45</t>
+          <t>2026-10-30 06:47</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55198,7 +55198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 06:47</t>
+          <t>2026-10-30 12:46</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55198,7 +55198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 12:46</t>
+          <t>2026-10-30 18:40</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55198,7 +55198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 18:40</t>
+          <t>2026-10-31 00:51</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55198,7 +55198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-31 00:51</t>
+          <t>2026-10-31 06:44</t>
         </is>
       </c>
     </row>

--- a/Gava_Joyeria_Catalogo.xlsx
+++ b/Gava_Joyeria_Catalogo.xlsx
@@ -55198,7 +55198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-31 06:44</t>
+          <t>2026-10-31 12:41</t>
         </is>
       </c>
     </row>
